--- a/research/traditional_assets/database/data/finland/finland_entertainment.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_entertainment.xlsx
@@ -1397,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1534,22 +1534,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09528736144608382</v>
+        <v>0.09513278672319164</v>
       </c>
       <c r="C2">
-        <v>7.836913872794831</v>
+        <v>7.767111766874571</v>
       </c>
       <c r="D2">
-        <v>5.436913872794832</v>
+        <v>5.447011766874572</v>
       </c>
       <c r="E2">
-        <v>-2.9</v>
+        <v>-2.8201</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0799</v>
       </c>
       <c r="G2">
         <v>2.4</v>
@@ -1570,28 +1570,28 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.004018969999999999</v>
       </c>
       <c r="N2">
-        <v>0.1522448979591835</v>
+        <v>0.1482259279591835</v>
       </c>
       <c r="O2">
-        <v>0.0304489795918367</v>
+        <v>0.0296451855918367</v>
       </c>
       <c r="P2">
-        <v>0.1217959183673468</v>
+        <v>0.1185807423673468</v>
       </c>
       <c r="Q2">
-        <v>2.081795918367347</v>
+        <v>2.078580742367347</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09528736144608382</v>
+        <v>0.0956872593163552</v>
       </c>
       <c r="T2">
-        <v>1.017512237681883</v>
+        <v>1.025734558794464</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>37.88157113867074</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1616,22 +1616,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09513278672319164</v>
+        <v>0.09497821200029948</v>
       </c>
       <c r="C3">
-        <v>7.767111766874571</v>
+        <v>7.697347240067088</v>
       </c>
       <c r="D3">
-        <v>5.447011766874572</v>
+        <v>5.457147240067088</v>
       </c>
       <c r="E3">
-        <v>-2.8201</v>
+        <v>-2.7402</v>
       </c>
       <c r="F3">
-        <v>0.0799</v>
+        <v>0.1598</v>
       </c>
       <c r="G3">
         <v>2.4</v>
@@ -1652,28 +1652,28 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M3">
-        <v>0.004018969999999999</v>
+        <v>0.008037939999999999</v>
       </c>
       <c r="N3">
-        <v>0.1482259279591835</v>
+        <v>0.1442069579591835</v>
       </c>
       <c r="O3">
-        <v>0.0296451855918367</v>
+        <v>0.0288413915918367</v>
       </c>
       <c r="P3">
-        <v>0.1185807423673468</v>
+        <v>0.1153655663673468</v>
       </c>
       <c r="Q3">
-        <v>2.078580742367347</v>
+        <v>2.075365566367347</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0956872593163552</v>
+        <v>0.09609531836765253</v>
       </c>
       <c r="T3">
-        <v>1.025734558794464</v>
+        <v>1.03412468237873</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>37.88157113867074</v>
+        <v>18.94078556933537</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1698,22 +1698,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09497821200029948</v>
+        <v>0.09485963727740732</v>
       </c>
       <c r="C4">
-        <v>7.697347240067088</v>
+        <v>7.625247792763701</v>
       </c>
       <c r="D4">
-        <v>5.457147240067088</v>
+        <v>5.464947792763701</v>
       </c>
       <c r="E4">
-        <v>-2.7402</v>
+        <v>-2.6603</v>
       </c>
       <c r="F4">
-        <v>0.1598</v>
+        <v>0.2397</v>
       </c>
       <c r="G4">
         <v>2.4</v>
@@ -1734,45 +1734,45 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M4">
-        <v>0.008037939999999999</v>
+        <v>0.01241646</v>
       </c>
       <c r="N4">
-        <v>0.1442069579591835</v>
+        <v>0.1398284379591835</v>
       </c>
       <c r="O4">
-        <v>0.0288413915918367</v>
+        <v>0.0279656875918367</v>
       </c>
       <c r="P4">
-        <v>0.1153655663673468</v>
+        <v>0.1118627503673468</v>
       </c>
       <c r="Q4">
-        <v>2.075365566367347</v>
+        <v>2.071862750367347</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09609531836765253</v>
+        <v>0.0965117910076364</v>
       </c>
       <c r="T4">
-        <v>1.03412468237873</v>
+        <v>1.042687798201847</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y4">
-        <v>18.94078556933537</v>
+        <v>12.26153814848866</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1780,22 +1780,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09485963727740732</v>
+        <v>0.09477146255451514</v>
       </c>
       <c r="C5">
-        <v>7.625247792763701</v>
+        <v>7.551162924845758</v>
       </c>
       <c r="D5">
-        <v>5.464947792763701</v>
+        <v>5.470762924845758</v>
       </c>
       <c r="E5">
-        <v>-2.6603</v>
+        <v>-2.5804</v>
       </c>
       <c r="F5">
-        <v>0.2397</v>
+        <v>0.3196</v>
       </c>
       <c r="G5">
         <v>2.4</v>
@@ -1816,45 +1816,45 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M5">
-        <v>0.01241646</v>
+        <v>0.0170986</v>
       </c>
       <c r="N5">
-        <v>0.1398284379591835</v>
+        <v>0.1351462979591835</v>
       </c>
       <c r="O5">
-        <v>0.0279656875918367</v>
+        <v>0.0270292595918367</v>
       </c>
       <c r="P5">
-        <v>0.1118627503673468</v>
+        <v>0.1081170383673468</v>
       </c>
       <c r="Q5">
-        <v>2.071862750367347</v>
+        <v>2.068117038367347</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0965117910076364</v>
+        <v>0.09693694016095328</v>
       </c>
       <c r="T5">
-        <v>1.042687798201847</v>
+        <v>1.051429312271279</v>
       </c>
       <c r="U5">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>12.26153814848866</v>
+        <v>8.903939384463261</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1862,22 +1862,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09477146255451514</v>
+        <v>0.09467448783162297</v>
       </c>
       <c r="C6">
-        <v>7.551162924845758</v>
+        <v>7.477672724371292</v>
       </c>
       <c r="D6">
-        <v>5.470762924845758</v>
+        <v>5.477172724371291</v>
       </c>
       <c r="E6">
-        <v>-2.5804</v>
+        <v>-2.5005</v>
       </c>
       <c r="F6">
-        <v>0.3196</v>
+        <v>0.3995</v>
       </c>
       <c r="G6">
         <v>2.4</v>
@@ -1898,45 +1898,45 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M6">
-        <v>0.0170986</v>
+        <v>0.02169285</v>
       </c>
       <c r="N6">
-        <v>0.1351462979591835</v>
+        <v>0.1305520479591835</v>
       </c>
       <c r="O6">
-        <v>0.0270292595918367</v>
+        <v>0.0261104095918367</v>
       </c>
       <c r="P6">
-        <v>0.1081170383673468</v>
+        <v>0.1044416383673468</v>
       </c>
       <c r="Q6">
-        <v>2.068117038367347</v>
+        <v>2.064441638367347</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09693694016095328</v>
+        <v>0.09737103982276102</v>
       </c>
       <c r="T6">
-        <v>1.051429312271279</v>
+        <v>1.060354858215856</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y6">
-        <v>8.903939384463261</v>
+        <v>7.018206365654281</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1944,22 +1944,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09467448783162297</v>
+        <v>0.09459991310873081</v>
       </c>
       <c r="C7">
-        <v>7.477672724371292</v>
+        <v>7.402712162722784</v>
       </c>
       <c r="D7">
-        <v>5.477172724371291</v>
+        <v>5.482112162722784</v>
       </c>
       <c r="E7">
-        <v>-2.5005</v>
+        <v>-2.4206</v>
       </c>
       <c r="F7">
-        <v>0.3995</v>
+        <v>0.4794</v>
       </c>
       <c r="G7">
         <v>2.4</v>
@@ -1980,45 +1980,45 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M7">
-        <v>0.02169285</v>
+        <v>0.02651082</v>
       </c>
       <c r="N7">
-        <v>0.1305520479591835</v>
+        <v>0.1257340779591835</v>
       </c>
       <c r="O7">
-        <v>0.0261104095918367</v>
+        <v>0.0251468155918367</v>
       </c>
       <c r="P7">
-        <v>0.1044416383673468</v>
+        <v>0.1005872623673468</v>
       </c>
       <c r="Q7">
-        <v>2.064441638367347</v>
+        <v>2.060587262367347</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09737103982276102</v>
+        <v>0.09781437564758597</v>
       </c>
       <c r="T7">
-        <v>1.060354858215856</v>
+        <v>1.069470309393298</v>
       </c>
       <c r="U7">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y7">
-        <v>7.018206365654281</v>
+        <v>5.742745715114942</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2026,22 +2026,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09459991310873081</v>
+        <v>0.09448533838583864</v>
       </c>
       <c r="C8">
-        <v>7.402712162722784</v>
+        <v>7.330418373662818</v>
       </c>
       <c r="D8">
-        <v>5.482112162722784</v>
+        <v>5.489718373662818</v>
       </c>
       <c r="E8">
-        <v>-2.4206</v>
+        <v>-2.3407</v>
       </c>
       <c r="F8">
-        <v>0.4794</v>
+        <v>0.5592999999999999</v>
       </c>
       <c r="G8">
         <v>2.4</v>
@@ -2062,28 +2062,28 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M8">
-        <v>0.02651082</v>
+        <v>0.03092928999999999</v>
       </c>
       <c r="N8">
-        <v>0.1257340779591835</v>
+        <v>0.1213156079591835</v>
       </c>
       <c r="O8">
-        <v>0.0251468155918367</v>
+        <v>0.0242631215918367</v>
       </c>
       <c r="P8">
-        <v>0.1005872623673468</v>
+        <v>0.0970524863673468</v>
       </c>
       <c r="Q8">
-        <v>2.060587262367347</v>
+        <v>2.057052486367347</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09781437564758597</v>
+        <v>0.09826724557617059</v>
       </c>
       <c r="T8">
-        <v>1.069470309393298</v>
+        <v>1.078781791778856</v>
       </c>
       <c r="U8">
         <v>0.0553</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>5.742745715114942</v>
+        <v>4.922353470098522</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2108,22 +2108,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09448533838583864</v>
+        <v>0.09453076366294647</v>
       </c>
       <c r="C9">
-        <v>7.330418373662818</v>
+        <v>7.247500226229302</v>
       </c>
       <c r="D9">
-        <v>5.489718373662818</v>
+        <v>5.486700226229302</v>
       </c>
       <c r="E9">
-        <v>-2.3407</v>
+        <v>-2.2608</v>
       </c>
       <c r="F9">
-        <v>0.5593</v>
+        <v>0.6392</v>
       </c>
       <c r="G9">
         <v>2.4</v>
@@ -2144,45 +2144,45 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M9">
-        <v>0.03092929</v>
+        <v>0.03694576</v>
       </c>
       <c r="N9">
-        <v>0.1213156079591835</v>
+        <v>0.1152991379591835</v>
       </c>
       <c r="O9">
-        <v>0.0242631215918367</v>
+        <v>0.0230598275918367</v>
       </c>
       <c r="P9">
-        <v>0.0970524863673468</v>
+        <v>0.09223931036734681</v>
       </c>
       <c r="Q9">
-        <v>2.057052486367347</v>
+        <v>2.052239310367347</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09826724557617059</v>
+        <v>0.09872996050320268</v>
       </c>
       <c r="T9">
-        <v>1.078781791778856</v>
+        <v>1.088295697694535</v>
       </c>
       <c r="U9">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y9">
-        <v>4.922353470098521</v>
+        <v>4.120767794712668</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2190,22 +2190,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09453076366294647</v>
+        <v>0.09488978894005431</v>
       </c>
       <c r="C10">
-        <v>7.247500226229302</v>
+        <v>7.143862122922438</v>
       </c>
       <c r="D10">
-        <v>5.486700226229302</v>
+        <v>5.462962122922438</v>
       </c>
       <c r="E10">
-        <v>-2.2608</v>
+        <v>-2.1809</v>
       </c>
       <c r="F10">
-        <v>0.6392</v>
+        <v>0.7191</v>
       </c>
       <c r="G10">
         <v>2.4</v>
@@ -2226,45 +2226,45 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M10">
-        <v>0.03694576</v>
+        <v>0.04609431</v>
       </c>
       <c r="N10">
-        <v>0.1152991379591835</v>
+        <v>0.1061505879591835</v>
       </c>
       <c r="O10">
-        <v>0.0230598275918367</v>
+        <v>0.0212301175918367</v>
       </c>
       <c r="P10">
-        <v>0.09223931036734681</v>
+        <v>0.0849204703673468</v>
       </c>
       <c r="Q10">
-        <v>2.052239310367347</v>
+        <v>2.044920470367347</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09872996050320268</v>
+        <v>0.09920284498907067</v>
       </c>
       <c r="T10">
-        <v>1.088295697694535</v>
+        <v>1.098018700443526</v>
       </c>
       <c r="U10">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.04624</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y10">
-        <v>4.120767794712668</v>
+        <v>3.302900031678172</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2272,22 +2272,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09488978894005431</v>
+        <v>0.09546961421716213</v>
       </c>
       <c r="C11">
-        <v>7.143862122922438</v>
+        <v>7.026055847443498</v>
       </c>
       <c r="D11">
-        <v>5.462962122922438</v>
+        <v>5.425055847443497</v>
       </c>
       <c r="E11">
-        <v>-2.1809</v>
+        <v>-2.101</v>
       </c>
       <c r="F11">
-        <v>0.7191</v>
+        <v>0.7989999999999999</v>
       </c>
       <c r="G11">
         <v>2.4</v>
@@ -2308,45 +2308,45 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M11">
-        <v>0.04609431</v>
+        <v>0.0574481</v>
       </c>
       <c r="N11">
-        <v>0.1061505879591835</v>
+        <v>0.0947967979591835</v>
       </c>
       <c r="O11">
-        <v>0.0212301175918367</v>
+        <v>0.0189593595918367</v>
       </c>
       <c r="P11">
-        <v>0.0849204703673468</v>
+        <v>0.0758374383673468</v>
       </c>
       <c r="Q11">
-        <v>2.044920470367347</v>
+        <v>2.035837438367347</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09920284498907067</v>
+        <v>0.09968623801906903</v>
       </c>
       <c r="T11">
-        <v>1.098018700443526</v>
+        <v>1.107957769920272</v>
       </c>
       <c r="U11">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>3.302900031678172</v>
+        <v>2.650129385639969</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09546961421716216</v>
+        <v>0.09583103949426998</v>
       </c>
       <c r="C12">
-        <v>7.026055847443495</v>
+        <v>6.922792548549092</v>
       </c>
       <c r="D12">
-        <v>5.425055847443495</v>
+        <v>5.401692548549092</v>
       </c>
       <c r="E12">
-        <v>-2.101</v>
+        <v>-2.0211</v>
       </c>
       <c r="F12">
-        <v>0.799</v>
+        <v>0.8789</v>
       </c>
       <c r="G12">
         <v>2.4</v>
@@ -2390,45 +2390,45 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M12">
-        <v>0.05744810000000001</v>
+        <v>0.06662062000000001</v>
       </c>
       <c r="N12">
-        <v>0.0947967979591835</v>
+        <v>0.0856242779591835</v>
       </c>
       <c r="O12">
-        <v>0.0189593595918367</v>
+        <v>0.0171248555918367</v>
       </c>
       <c r="P12">
-        <v>0.0758374383673468</v>
+        <v>0.0684994223673468</v>
       </c>
       <c r="Q12">
-        <v>2.035837438367347</v>
+        <v>2.028499422367347</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09968623801906905</v>
+        <v>0.1001804938137865</v>
       </c>
       <c r="T12">
-        <v>1.107957769920272</v>
+        <v>1.1181201892729</v>
       </c>
       <c r="U12">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y12">
-        <v>2.650129385639969</v>
+        <v>2.285251892870158</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2436,22 +2436,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09583103949426998</v>
+        <v>0.09588046477137782</v>
       </c>
       <c r="C13">
-        <v>6.922792548549092</v>
+        <v>6.839713225111447</v>
       </c>
       <c r="D13">
-        <v>5.401692548549092</v>
+        <v>5.398513225111447</v>
       </c>
       <c r="E13">
-        <v>-2.0211</v>
+        <v>-1.9412</v>
       </c>
       <c r="F13">
-        <v>0.8789</v>
+        <v>0.9588</v>
       </c>
       <c r="G13">
         <v>2.4</v>
@@ -2472,28 +2472,28 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M13">
-        <v>0.06662062000000001</v>
+        <v>0.07267704</v>
       </c>
       <c r="N13">
-        <v>0.0856242779591835</v>
+        <v>0.0795678579591835</v>
       </c>
       <c r="O13">
-        <v>0.0171248555918367</v>
+        <v>0.0159135715918367</v>
       </c>
       <c r="P13">
-        <v>0.0684994223673468</v>
+        <v>0.0636542863673468</v>
       </c>
       <c r="Q13">
-        <v>2.028499422367347</v>
+        <v>2.023654286367347</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1001804938137865</v>
+        <v>0.1006859826947475</v>
       </c>
       <c r="T13">
-        <v>1.1181201892729</v>
+        <v>1.128513572701724</v>
       </c>
       <c r="U13">
         <v>0.07580000000000001</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>2.285251892870158</v>
+        <v>2.094814235130978</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2518,22 +2518,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09588046477137782</v>
+        <v>0.09740669004848565</v>
       </c>
       <c r="C14">
-        <v>6.839713225111447</v>
+        <v>6.663446717476869</v>
       </c>
       <c r="D14">
-        <v>5.398513225111447</v>
+        <v>5.302146717476869</v>
       </c>
       <c r="E14">
-        <v>-1.9412</v>
+        <v>-1.8613</v>
       </c>
       <c r="F14">
-        <v>0.9588</v>
+        <v>1.0387</v>
       </c>
       <c r="G14">
         <v>2.4</v>
@@ -2554,45 +2554,45 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M14">
-        <v>0.07267704</v>
+        <v>0.093483</v>
       </c>
       <c r="N14">
-        <v>0.0795678579591835</v>
+        <v>0.0587618979591835</v>
       </c>
       <c r="O14">
-        <v>0.0159135715918367</v>
+        <v>0.0117523795918367</v>
       </c>
       <c r="P14">
-        <v>0.0636542863673468</v>
+        <v>0.04700951836734681</v>
       </c>
       <c r="Q14">
-        <v>2.023654286367347</v>
+        <v>2.007009518367347</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1006859826947475</v>
+        <v>0.1012030920097536</v>
       </c>
       <c r="T14">
-        <v>1.128513572701724</v>
+        <v>1.139145884485234</v>
       </c>
       <c r="U14">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>2.094814235130978</v>
+        <v>1.628583784850545</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2600,22 +2600,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09740669004848565</v>
+        <v>0.09756971532559347</v>
       </c>
       <c r="C15">
-        <v>6.663446717476869</v>
+        <v>6.573456217059197</v>
       </c>
       <c r="D15">
-        <v>5.302146717476869</v>
+        <v>5.292056217059196</v>
       </c>
       <c r="E15">
-        <v>-1.8613</v>
+        <v>-1.7814</v>
       </c>
       <c r="F15">
-        <v>1.0387</v>
+        <v>1.1186</v>
       </c>
       <c r="G15">
         <v>2.4</v>
@@ -2636,28 +2636,28 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M15">
-        <v>0.093483</v>
+        <v>0.100674</v>
       </c>
       <c r="N15">
-        <v>0.0587618979591835</v>
+        <v>0.0515708979591835</v>
       </c>
       <c r="O15">
-        <v>0.0117523795918367</v>
+        <v>0.0103141795918367</v>
       </c>
       <c r="P15">
-        <v>0.04700951836734681</v>
+        <v>0.0412567183673468</v>
       </c>
       <c r="Q15">
-        <v>2.007009518367347</v>
+        <v>2.001256718367347</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1012030920097536</v>
+        <v>0.1017322271227831</v>
       </c>
       <c r="T15">
-        <v>1.139145884485234</v>
+        <v>1.150025459333477</v>
       </c>
       <c r="U15">
         <v>0.09</v>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>1.628583784850545</v>
+        <v>1.512256371646935</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2682,22 +2682,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09756971532559347</v>
+        <v>0.1053417976258391</v>
       </c>
       <c r="C16">
-        <v>6.573456217059197</v>
+        <v>6.053355017015664</v>
       </c>
       <c r="D16">
-        <v>5.292056217059196</v>
+        <v>4.851855017015664</v>
       </c>
       <c r="E16">
-        <v>-1.7814</v>
+        <v>-1.7015</v>
       </c>
       <c r="F16">
-        <v>1.1186</v>
+        <v>1.1985</v>
       </c>
       <c r="G16">
         <v>2.4</v>
@@ -2718,45 +2718,45 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M16">
-        <v>0.100674</v>
+        <v>0.1759398</v>
       </c>
       <c r="N16">
-        <v>0.0515708979591835</v>
+        <v>-0.02369490204081653</v>
       </c>
       <c r="O16">
-        <v>0.0103141795918367</v>
+        <v>-0.004738980408163307</v>
       </c>
       <c r="P16">
-        <v>0.0412567183673468</v>
+        <v>-0.01895592163265323</v>
       </c>
       <c r="Q16">
-        <v>2.001256718367347</v>
+        <v>1.941044078367347</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1017322271227831</v>
+        <v>0.1025090396263404</v>
       </c>
       <c r="T16">
-        <v>1.150025459333477</v>
+        <v>1.165997542015942</v>
       </c>
       <c r="U16">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V16">
-        <v>0.2</v>
+        <v>0.1730647618778508</v>
       </c>
       <c r="W16">
-        <v>0.07199999999999999</v>
+        <v>0.1213940929563315</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y16">
-        <v>1.512256371646935</v>
+        <v>0.865323809389254</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2764,22 +2764,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1053417976258391</v>
+        <v>0.1063517976258391</v>
       </c>
       <c r="C17">
-        <v>6.053355017015664</v>
+        <v>5.92156913533864</v>
       </c>
       <c r="D17">
-        <v>4.851855017015664</v>
+        <v>4.79996913533864</v>
       </c>
       <c r="E17">
-        <v>-1.7015</v>
+        <v>-1.6216</v>
       </c>
       <c r="F17">
-        <v>1.1985</v>
+        <v>1.2784</v>
       </c>
       <c r="G17">
         <v>2.4</v>
@@ -2800,37 +2800,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M17">
-        <v>0.1759398</v>
+        <v>0.18766912</v>
       </c>
       <c r="N17">
-        <v>-0.02369490204081651</v>
+        <v>-0.03542422204081652</v>
       </c>
       <c r="O17">
-        <v>-0.004738980408163302</v>
+        <v>-0.007084844408163305</v>
       </c>
       <c r="P17">
-        <v>-0.0189559216326532</v>
+        <v>-0.02833937763265322</v>
       </c>
       <c r="Q17">
-        <v>1.941044078367347</v>
+        <v>1.931660622367347</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1025090396263404</v>
+        <v>0.1031841472409397</v>
       </c>
       <c r="T17">
-        <v>1.165997542015942</v>
+        <v>1.179878465135179</v>
       </c>
       <c r="U17">
         <v>0.1468</v>
       </c>
       <c r="V17">
-        <v>0.1730647618778508</v>
+        <v>0.1622482142604852</v>
       </c>
       <c r="W17">
-        <v>0.1213940929563315</v>
+        <v>0.1229819621465608</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.8653238093892541</v>
+        <v>0.8112410713024256</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2846,22 +2846,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1063517976258391</v>
+        <v>0.116887278697749</v>
       </c>
       <c r="C18">
-        <v>5.92156913533864</v>
+        <v>5.359961707947281</v>
       </c>
       <c r="D18">
-        <v>4.79996913533864</v>
+        <v>4.318261707947281</v>
       </c>
       <c r="E18">
-        <v>-1.6216</v>
+        <v>-1.5417</v>
       </c>
       <c r="F18">
-        <v>1.2784</v>
+        <v>1.3583</v>
       </c>
       <c r="G18">
         <v>2.4</v>
@@ -2882,45 +2882,45 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M18">
-        <v>0.18766912</v>
+        <v>0.27274664</v>
       </c>
       <c r="N18">
-        <v>-0.03542422204081652</v>
+        <v>-0.1205017420408165</v>
       </c>
       <c r="O18">
-        <v>-0.007084844408163305</v>
+        <v>-0.02410034840816331</v>
       </c>
       <c r="P18">
-        <v>-0.02833937763265322</v>
+        <v>-0.09640139363265324</v>
       </c>
       <c r="Q18">
-        <v>1.931660622367347</v>
+        <v>1.863598606367347</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1031841472409397</v>
+        <v>0.1042917647642159</v>
       </c>
       <c r="T18">
-        <v>1.179878465135179</v>
+        <v>1.20265224720138</v>
       </c>
       <c r="U18">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V18">
-        <v>0.1622482142604852</v>
+        <v>0.1116383306934109</v>
       </c>
       <c r="W18">
-        <v>0.1229819621465608</v>
+        <v>0.1783830231967631</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y18">
-        <v>0.8112410713024256</v>
+        <v>0.5581916534670546</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2928,22 +2928,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.116887278697749</v>
+        <v>0.118437278697749</v>
       </c>
       <c r="C19">
-        <v>5.359961707947281</v>
+        <v>5.217231880389797</v>
       </c>
       <c r="D19">
-        <v>4.318261707947281</v>
+        <v>4.255431880389796</v>
       </c>
       <c r="E19">
-        <v>-1.5417</v>
+        <v>-1.4618</v>
       </c>
       <c r="F19">
-        <v>1.3583</v>
+        <v>1.4382</v>
       </c>
       <c r="G19">
         <v>2.4</v>
@@ -2964,37 +2964,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M19">
-        <v>0.27274664</v>
+        <v>0.28879056</v>
       </c>
       <c r="N19">
-        <v>-0.1205017420408165</v>
+        <v>-0.1365456620408165</v>
       </c>
       <c r="O19">
-        <v>-0.02410034840816331</v>
+        <v>-0.02730913240816331</v>
       </c>
       <c r="P19">
-        <v>-0.09640139363265324</v>
+        <v>-0.1092365296326532</v>
       </c>
       <c r="Q19">
-        <v>1.863598606367347</v>
+        <v>1.850763470367347</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1042917647642159</v>
+        <v>0.1050050789686576</v>
       </c>
       <c r="T19">
-        <v>1.20265224720138</v>
+        <v>1.21731873802091</v>
       </c>
       <c r="U19">
         <v>0.2008</v>
       </c>
       <c r="V19">
-        <v>0.1116383306934109</v>
+        <v>0.1054362012104436</v>
       </c>
       <c r="W19">
-        <v>0.1783830231967631</v>
+        <v>0.1796284107969429</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.5581916534670546</v>
+        <v>0.5271810060522182</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3010,22 +3010,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.118437278697749</v>
+        <v>0.1267766844832132</v>
       </c>
       <c r="C20">
-        <v>5.217231880389795</v>
+        <v>4.82839360329889</v>
       </c>
       <c r="D20">
-        <v>4.255431880389795</v>
+        <v>3.94649360329889</v>
       </c>
       <c r="E20">
-        <v>-1.4618</v>
+        <v>-1.3819</v>
       </c>
       <c r="F20">
-        <v>1.4382</v>
+        <v>1.5181</v>
       </c>
       <c r="G20">
         <v>2.4</v>
@@ -3046,45 +3046,45 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M20">
-        <v>0.28879056</v>
+        <v>0.35796798</v>
       </c>
       <c r="N20">
-        <v>-0.1365456620408165</v>
+        <v>-0.2057230820408165</v>
       </c>
       <c r="O20">
-        <v>-0.02730913240816329</v>
+        <v>-0.0411446164081633</v>
       </c>
       <c r="P20">
-        <v>-0.1092365296326532</v>
+        <v>-0.1645784656326532</v>
       </c>
       <c r="Q20">
-        <v>1.850763470367347</v>
+        <v>1.795421534367347</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1050050789686576</v>
+        <v>0.1059081117774857</v>
       </c>
       <c r="T20">
-        <v>1.217318738020909</v>
+        <v>1.235886043028915</v>
       </c>
       <c r="U20">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.1054362012104437</v>
+        <v>0.08506062355587418</v>
       </c>
       <c r="W20">
-        <v>0.1796284107969429</v>
+        <v>0.2157427049655249</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y20">
-        <v>0.5271810060522183</v>
+        <v>0.4253031177793709</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3092,22 +3092,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1267766844832132</v>
+        <v>0.1286766844832132</v>
       </c>
       <c r="C21">
-        <v>4.82839360329889</v>
+        <v>4.684279071196895</v>
       </c>
       <c r="D21">
-        <v>3.94649360329889</v>
+        <v>3.882279071196895</v>
       </c>
       <c r="E21">
-        <v>-1.3819</v>
+        <v>-1.302</v>
       </c>
       <c r="F21">
-        <v>1.5181</v>
+        <v>1.598</v>
       </c>
       <c r="G21">
         <v>2.4</v>
@@ -3128,37 +3128,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M21">
-        <v>0.35796798</v>
+        <v>0.3768084</v>
       </c>
       <c r="N21">
-        <v>-0.2057230820408165</v>
+        <v>-0.2245635020408165</v>
       </c>
       <c r="O21">
-        <v>-0.0411446164081633</v>
+        <v>-0.04491270040816331</v>
       </c>
       <c r="P21">
-        <v>-0.1645784656326532</v>
+        <v>-0.1796508016326532</v>
       </c>
       <c r="Q21">
-        <v>1.795421534367347</v>
+        <v>1.780349198367347</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1059081117774857</v>
+        <v>0.1066594631747043</v>
       </c>
       <c r="T21">
-        <v>1.235886043028915</v>
+        <v>1.251334618566777</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.08506062355587418</v>
+        <v>0.08080759237808048</v>
       </c>
       <c r="W21">
-        <v>0.2157427049655249</v>
+        <v>0.2167455697172486</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.4253031177793709</v>
+        <v>0.4040379618904023</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3174,22 +3174,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1286766844832132</v>
+        <v>0.1305766844832132</v>
       </c>
       <c r="C22">
-        <v>4.684279071196895</v>
+        <v>4.542220787514814</v>
       </c>
       <c r="D22">
-        <v>3.882279071196895</v>
+        <v>3.820120787514814</v>
       </c>
       <c r="E22">
-        <v>-1.302</v>
+        <v>-1.2221</v>
       </c>
       <c r="F22">
-        <v>1.598</v>
+        <v>1.6779</v>
       </c>
       <c r="G22">
         <v>2.4</v>
@@ -3210,37 +3210,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M22">
-        <v>0.3768084</v>
+        <v>0.3956488200000001</v>
       </c>
       <c r="N22">
-        <v>-0.2245635020408165</v>
+        <v>-0.2434039220408166</v>
       </c>
       <c r="O22">
-        <v>-0.04491270040816331</v>
+        <v>-0.04868078440816331</v>
       </c>
       <c r="P22">
-        <v>-0.1796508016326532</v>
+        <v>-0.1947231376326533</v>
       </c>
       <c r="Q22">
-        <v>1.780349198367347</v>
+        <v>1.765276862367347</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1066594631747043</v>
+        <v>0.1074298361262828</v>
       </c>
       <c r="T22">
-        <v>1.251334618566777</v>
+        <v>1.267174297282812</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.08080759237808048</v>
+        <v>0.07695961178864807</v>
       </c>
       <c r="W22">
-        <v>0.2167455697172486</v>
+        <v>0.2176529235402368</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.4040379618904023</v>
+        <v>0.3847980589432403</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3256,22 +3256,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1305766844832132</v>
+        <v>0.1324766844832131</v>
       </c>
       <c r="C23">
-        <v>4.542220787514814</v>
+        <v>4.402121542287496</v>
       </c>
       <c r="D23">
-        <v>3.820120787514814</v>
+        <v>3.759921542287495</v>
       </c>
       <c r="E23">
-        <v>-1.2221</v>
+        <v>-1.1422</v>
       </c>
       <c r="F23">
-        <v>1.6779</v>
+        <v>1.7578</v>
       </c>
       <c r="G23">
         <v>2.4</v>
@@ -3292,37 +3292,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M23">
-        <v>0.39564882</v>
+        <v>0.41448924</v>
       </c>
       <c r="N23">
-        <v>-0.2434039220408165</v>
+        <v>-0.2622443420408165</v>
       </c>
       <c r="O23">
-        <v>-0.04868078440816331</v>
+        <v>-0.05244886840816331</v>
       </c>
       <c r="P23">
-        <v>-0.1947231376326532</v>
+        <v>-0.2097954736326532</v>
       </c>
       <c r="Q23">
-        <v>1.765276862367347</v>
+        <v>1.750204526367347</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1074298361262828</v>
+        <v>0.1082199622304659</v>
       </c>
       <c r="T23">
-        <v>1.267174297282812</v>
+        <v>1.28342012160695</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.07695961178864807</v>
+        <v>0.07346144761643679</v>
       </c>
       <c r="W23">
-        <v>0.2176529235402368</v>
+        <v>0.2184777906520442</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.3847980589432404</v>
+        <v>0.3673072380821839</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3338,22 +3338,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1324766844832131</v>
+        <v>0.1343766844832132</v>
       </c>
       <c r="C24">
-        <v>4.402121542287496</v>
+        <v>4.263890158007396</v>
       </c>
       <c r="D24">
-        <v>3.759921542287495</v>
+        <v>3.701590158007396</v>
       </c>
       <c r="E24">
-        <v>-1.1422</v>
+        <v>-1.0623</v>
       </c>
       <c r="F24">
-        <v>1.7578</v>
+        <v>1.8377</v>
       </c>
       <c r="G24">
         <v>2.4</v>
@@ -3374,37 +3374,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M24">
-        <v>0.41448924</v>
+        <v>0.4333296600000001</v>
       </c>
       <c r="N24">
-        <v>-0.2622443420408165</v>
+        <v>-0.2810847620408166</v>
       </c>
       <c r="O24">
-        <v>-0.05244886840816331</v>
+        <v>-0.05621695240816332</v>
       </c>
       <c r="P24">
-        <v>-0.2097954736326532</v>
+        <v>-0.2248678096326532</v>
       </c>
       <c r="Q24">
-        <v>1.750204526367347</v>
+        <v>1.735132190367347</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1082199622304659</v>
+        <v>0.1090306110906019</v>
       </c>
       <c r="T24">
-        <v>1.28342012160695</v>
+        <v>1.300087915394054</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.07346144761643679</v>
+        <v>0.07026747163311346</v>
       </c>
       <c r="W24">
-        <v>0.2184777906520442</v>
+        <v>0.2192309301889119</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.3673072380821839</v>
+        <v>0.3513373581655672</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3420,22 +3420,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1343766844832132</v>
+        <v>0.1362766844832132</v>
       </c>
       <c r="C25">
-        <v>4.263890158007396</v>
+        <v>4.127441028835834</v>
       </c>
       <c r="D25">
-        <v>3.701590158007396</v>
+        <v>3.645041028835835</v>
       </c>
       <c r="E25">
-        <v>-1.0623</v>
+        <v>-0.9823999999999997</v>
       </c>
       <c r="F25">
-        <v>1.8377</v>
+        <v>1.9176</v>
       </c>
       <c r="G25">
         <v>2.4</v>
@@ -3456,37 +3456,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M25">
-        <v>0.4333296600000001</v>
+        <v>0.4521700800000001</v>
       </c>
       <c r="N25">
-        <v>-0.2810847620408166</v>
+        <v>-0.2999251820408166</v>
       </c>
       <c r="O25">
-        <v>-0.05621695240816332</v>
+        <v>-0.05998503640816332</v>
       </c>
       <c r="P25">
-        <v>-0.2248678096326532</v>
+        <v>-0.2399401456326533</v>
       </c>
       <c r="Q25">
-        <v>1.735132190367347</v>
+        <v>1.720059854367347</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1090306110906019</v>
+        <v>0.1098625928154782</v>
       </c>
       <c r="T25">
-        <v>1.300087915394054</v>
+        <v>1.317194335333449</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.07026747163311346</v>
+        <v>0.06733966031506705</v>
       </c>
       <c r="W25">
-        <v>0.2192309301889119</v>
+        <v>0.2199213080977072</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3513373581655672</v>
+        <v>0.3366983015753353</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3502,22 +3502,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1362766844832132</v>
+        <v>0.1381766844832132</v>
       </c>
       <c r="C26">
-        <v>4.127441028835834</v>
+        <v>3.99269370141546</v>
       </c>
       <c r="D26">
-        <v>3.645041028835835</v>
+        <v>3.590193701415461</v>
       </c>
       <c r="E26">
-        <v>-0.9823999999999999</v>
+        <v>-0.9024999999999999</v>
       </c>
       <c r="F26">
-        <v>1.9176</v>
+        <v>1.9975</v>
       </c>
       <c r="G26">
         <v>2.4</v>
@@ -3538,37 +3538,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M26">
-        <v>0.45217008</v>
+        <v>0.4710105000000001</v>
       </c>
       <c r="N26">
-        <v>-0.2999251820408165</v>
+        <v>-0.3187656020408166</v>
       </c>
       <c r="O26">
-        <v>-0.05998503640816331</v>
+        <v>-0.06375312040816332</v>
       </c>
       <c r="P26">
-        <v>-0.2399401456326532</v>
+        <v>-0.2550124816326532</v>
       </c>
       <c r="Q26">
-        <v>1.720059854367347</v>
+        <v>1.704987518367347</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1098625928154782</v>
+        <v>0.1107167607196846</v>
       </c>
       <c r="T26">
-        <v>1.317194335333449</v>
+        <v>1.334756926471228</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.06733966031506707</v>
+        <v>0.06464607390246438</v>
       </c>
       <c r="W26">
-        <v>0.2199213080977072</v>
+        <v>0.2205564557737989</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.3366983015753353</v>
+        <v>0.3232303695123219</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3584,22 +3584,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1381766844832132</v>
+        <v>0.1400766844832132</v>
       </c>
       <c r="C27">
-        <v>3.99269370141546</v>
+        <v>3.859572492967066</v>
       </c>
       <c r="D27">
-        <v>3.590193701415461</v>
+        <v>3.536972492967066</v>
       </c>
       <c r="E27">
-        <v>-0.9024999999999999</v>
+        <v>-0.8226</v>
       </c>
       <c r="F27">
-        <v>1.9975</v>
+        <v>2.0774</v>
       </c>
       <c r="G27">
         <v>2.4</v>
@@ -3620,37 +3620,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M27">
-        <v>0.4710105000000001</v>
+        <v>0.48985092</v>
       </c>
       <c r="N27">
-        <v>-0.3187656020408166</v>
+        <v>-0.3376060220408165</v>
       </c>
       <c r="O27">
-        <v>-0.06375312040816332</v>
+        <v>-0.06752120440816331</v>
       </c>
       <c r="P27">
-        <v>-0.2550124816326532</v>
+        <v>-0.2700848176326532</v>
       </c>
       <c r="Q27">
-        <v>1.704987518367347</v>
+        <v>1.689915182367347</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1107167607196846</v>
+        <v>0.1115940142429236</v>
       </c>
       <c r="T27">
-        <v>1.334756926471228</v>
+        <v>1.352794182234353</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.06464607390246438</v>
+        <v>0.06215968644467729</v>
       </c>
       <c r="W27">
-        <v>0.2205564557737989</v>
+        <v>0.2211427459363451</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.3232303695123219</v>
+        <v>0.3107984322233864</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3666,22 +3666,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1400766844832132</v>
+        <v>0.1419766844832132</v>
       </c>
       <c r="C28">
-        <v>3.859572492967066</v>
+        <v>3.728006142858322</v>
       </c>
       <c r="D28">
-        <v>3.536972492967066</v>
+        <v>3.485306142858323</v>
       </c>
       <c r="E28">
-        <v>-0.8226</v>
+        <v>-0.7426999999999997</v>
       </c>
       <c r="F28">
-        <v>2.0774</v>
+        <v>2.1573</v>
       </c>
       <c r="G28">
         <v>2.4</v>
@@ -3702,37 +3702,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M28">
-        <v>0.48985092</v>
+        <v>0.50869134</v>
       </c>
       <c r="N28">
-        <v>-0.3376060220408165</v>
+        <v>-0.3564464420408165</v>
       </c>
       <c r="O28">
-        <v>-0.06752120440816331</v>
+        <v>-0.07128928840816331</v>
       </c>
       <c r="P28">
-        <v>-0.2700848176326532</v>
+        <v>-0.2851571536326533</v>
       </c>
       <c r="Q28">
-        <v>1.689915182367347</v>
+        <v>1.674842846367347</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1115940142429236</v>
+        <v>0.112495302109265</v>
       </c>
       <c r="T28">
-        <v>1.352794182234353</v>
+        <v>1.371325609388248</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.06215968644467729</v>
+        <v>0.05985747583561516</v>
       </c>
       <c r="W28">
-        <v>0.2211427459363451</v>
+        <v>0.221685607197962</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.3107984322233864</v>
+        <v>0.2992873791780758</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3748,22 +3748,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1419766844832132</v>
+        <v>0.1438766844832132</v>
       </c>
       <c r="C29">
-        <v>3.728006142858322</v>
+        <v>3.597927494271125</v>
       </c>
       <c r="D29">
-        <v>3.485306142858323</v>
+        <v>3.435127494271125</v>
       </c>
       <c r="E29">
-        <v>-0.7426999999999997</v>
+        <v>-0.6627999999999998</v>
       </c>
       <c r="F29">
-        <v>2.1573</v>
+        <v>2.2372</v>
       </c>
       <c r="G29">
         <v>2.4</v>
@@ -3784,37 +3784,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M29">
-        <v>0.50869134</v>
+        <v>0.52753176</v>
       </c>
       <c r="N29">
-        <v>-0.3564464420408165</v>
+        <v>-0.3752868620408165</v>
       </c>
       <c r="O29">
-        <v>-0.07128928840816331</v>
+        <v>-0.07505737240816331</v>
       </c>
       <c r="P29">
-        <v>-0.2851571536326533</v>
+        <v>-0.3002294896326532</v>
       </c>
       <c r="Q29">
-        <v>1.674842846367347</v>
+        <v>1.659770510367347</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.112495302109265</v>
+        <v>0.1134216257496714</v>
       </c>
       <c r="T29">
-        <v>1.371325609388248</v>
+        <v>1.39037179840753</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.05985747583561516</v>
+        <v>0.05771970884148606</v>
       </c>
       <c r="W29">
-        <v>0.221685607197962</v>
+        <v>0.2221896926551776</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2992873791780758</v>
+        <v>0.2885985442074303</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3830,22 +3830,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1438766844832132</v>
+        <v>0.1457766844832132</v>
       </c>
       <c r="C30">
-        <v>3.597927494271125</v>
+        <v>3.469273202977235</v>
       </c>
       <c r="D30">
-        <v>3.435127494271125</v>
+        <v>3.386373202977235</v>
       </c>
       <c r="E30">
-        <v>-0.6627999999999998</v>
+        <v>-0.5828999999999995</v>
       </c>
       <c r="F30">
-        <v>2.2372</v>
+        <v>2.3171</v>
       </c>
       <c r="G30">
         <v>2.4</v>
@@ -3866,37 +3866,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M30">
-        <v>0.52753176</v>
+        <v>0.5463721800000001</v>
       </c>
       <c r="N30">
-        <v>-0.3752868620408165</v>
+        <v>-0.3941272820408166</v>
       </c>
       <c r="O30">
-        <v>-0.07505737240816331</v>
+        <v>-0.07882545640816332</v>
       </c>
       <c r="P30">
-        <v>-0.3002294896326532</v>
+        <v>-0.3153018256326533</v>
       </c>
       <c r="Q30">
-        <v>1.659770510367347</v>
+        <v>1.644698174367347</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1134216257496714</v>
+        <v>0.1143740430137513</v>
       </c>
       <c r="T30">
-        <v>1.39037179840753</v>
+        <v>1.409954499793551</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.05771970884148606</v>
+        <v>0.05572937405384859</v>
       </c>
       <c r="W30">
-        <v>0.2221896926551776</v>
+        <v>0.2226590135981025</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2885985442074303</v>
+        <v>0.278646870269243</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3912,22 +3912,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1457766844832132</v>
+        <v>0.1476766844832131</v>
       </c>
       <c r="C31">
-        <v>3.469273202977236</v>
+        <v>3.341983470566726</v>
       </c>
       <c r="D31">
-        <v>3.386373202977236</v>
+        <v>3.338983470566726</v>
       </c>
       <c r="E31">
-        <v>-0.5829</v>
+        <v>-0.5030000000000001</v>
       </c>
       <c r="F31">
-        <v>2.3171</v>
+        <v>2.397</v>
       </c>
       <c r="G31">
         <v>2.4</v>
@@ -3948,37 +3948,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M31">
-        <v>0.54637218</v>
+        <v>0.5652126</v>
       </c>
       <c r="N31">
-        <v>-0.3941272820408165</v>
+        <v>-0.4129677020408165</v>
       </c>
       <c r="O31">
-        <v>-0.0788254564081633</v>
+        <v>-0.0825935404081633</v>
       </c>
       <c r="P31">
-        <v>-0.3153018256326532</v>
+        <v>-0.3303741616326532</v>
       </c>
       <c r="Q31">
-        <v>1.644698174367347</v>
+        <v>1.629625838367347</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1143740430137513</v>
+        <v>0.1153536721996621</v>
       </c>
       <c r="T31">
-        <v>1.409954499793551</v>
+        <v>1.430096706933459</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.05572937405384862</v>
+        <v>0.05387172825205366</v>
       </c>
       <c r="W31">
-        <v>0.2226590135981025</v>
+        <v>0.2230970464781658</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2786468702692431</v>
+        <v>0.2693586412602683</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3994,22 +3994,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1476766844832131</v>
+        <v>0.1495766844832132</v>
       </c>
       <c r="C32">
-        <v>3.341983470566726</v>
+        <v>3.216001799766874</v>
       </c>
       <c r="D32">
-        <v>3.338983470566726</v>
+        <v>3.292901799766874</v>
       </c>
       <c r="E32">
-        <v>-0.5030000000000001</v>
+        <v>-0.4230999999999998</v>
       </c>
       <c r="F32">
-        <v>2.397</v>
+        <v>2.4769</v>
       </c>
       <c r="G32">
         <v>2.4</v>
@@ -4030,37 +4030,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M32">
-        <v>0.5652126</v>
+        <v>0.58405302</v>
       </c>
       <c r="N32">
-        <v>-0.4129677020408165</v>
+        <v>-0.4318081220408165</v>
       </c>
       <c r="O32">
-        <v>-0.0825935404081633</v>
+        <v>-0.08636162440816331</v>
       </c>
       <c r="P32">
-        <v>-0.3303741616326532</v>
+        <v>-0.3454464976326532</v>
       </c>
       <c r="Q32">
-        <v>1.629625838367347</v>
+        <v>1.614553502367347</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1153536721996621</v>
+        <v>0.1163616964344398</v>
       </c>
       <c r="T32">
-        <v>1.430096706933459</v>
+        <v>1.450822746164379</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.05387172825205366</v>
+        <v>0.05213393056650353</v>
       </c>
       <c r="W32">
-        <v>0.2230970464781658</v>
+        <v>0.2235068191724185</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2693586412602683</v>
+        <v>0.2606696528325176</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4076,22 +4076,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1495766844832132</v>
+        <v>0.1514766844832132</v>
       </c>
       <c r="C33">
-        <v>3.216001799766874</v>
+        <v>3.091274769746459</v>
       </c>
       <c r="D33">
-        <v>3.292901799766874</v>
+        <v>3.248074769746459</v>
       </c>
       <c r="E33">
-        <v>-0.4230999999999998</v>
+        <v>-0.3431999999999999</v>
       </c>
       <c r="F33">
-        <v>2.4769</v>
+        <v>2.5568</v>
       </c>
       <c r="G33">
         <v>2.4</v>
@@ -4112,37 +4112,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M33">
-        <v>0.58405302</v>
+        <v>0.60289344</v>
       </c>
       <c r="N33">
-        <v>-0.4318081220408165</v>
+        <v>-0.4506485420408165</v>
       </c>
       <c r="O33">
-        <v>-0.08636162440816331</v>
+        <v>-0.09012970840816331</v>
       </c>
       <c r="P33">
-        <v>-0.3454464976326532</v>
+        <v>-0.3605188336326532</v>
       </c>
       <c r="Q33">
-        <v>1.614553502367347</v>
+        <v>1.599481166367347</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1163616964344398</v>
+        <v>0.1173993684408286</v>
       </c>
       <c r="T33">
-        <v>1.450822746164379</v>
+        <v>1.472158374784443</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.05213393056650353</v>
+        <v>0.0505047452363003</v>
       </c>
       <c r="W33">
-        <v>0.2235068191724185</v>
+        <v>0.2238909810732804</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2606696528325176</v>
+        <v>0.2525237261815015</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4158,22 +4158,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1514766844832132</v>
+        <v>0.1533766844832132</v>
       </c>
       <c r="C34">
-        <v>3.091274769746459</v>
+        <v>2.967751829526581</v>
       </c>
       <c r="D34">
-        <v>3.248074769746459</v>
+        <v>3.204451829526581</v>
       </c>
       <c r="E34">
-        <v>-0.3431999999999999</v>
+        <v>-0.2632999999999996</v>
       </c>
       <c r="F34">
-        <v>2.5568</v>
+        <v>2.6367</v>
       </c>
       <c r="G34">
         <v>2.4</v>
@@ -4194,37 +4194,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M34">
-        <v>0.60289344</v>
+        <v>0.6217338600000001</v>
       </c>
       <c r="N34">
-        <v>-0.4506485420408165</v>
+        <v>-0.4694889620408166</v>
       </c>
       <c r="O34">
-        <v>-0.09012970840816331</v>
+        <v>-0.09389779240816332</v>
       </c>
       <c r="P34">
-        <v>-0.3605188336326532</v>
+        <v>-0.3755911696326533</v>
       </c>
       <c r="Q34">
-        <v>1.599481166367347</v>
+        <v>1.584408830367347</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1173993684408286</v>
+        <v>0.1184680157309902</v>
       </c>
       <c r="T34">
-        <v>1.472158374784443</v>
+        <v>1.494130887840927</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.0505047452363003</v>
+        <v>0.04897429841095786</v>
       </c>
       <c r="W34">
-        <v>0.2238909810732804</v>
+        <v>0.2242518604346961</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2525237261815015</v>
+        <v>0.2448714920547893</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4240,22 +4240,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1533766844832132</v>
+        <v>0.1552766844832132</v>
       </c>
       <c r="C35">
-        <v>2.967751829526581</v>
+        <v>2.845385107818303</v>
       </c>
       <c r="D35">
-        <v>3.204451829526581</v>
+        <v>3.161985107818304</v>
       </c>
       <c r="E35">
-        <v>-0.2632999999999996</v>
+        <v>-0.1833999999999998</v>
       </c>
       <c r="F35">
-        <v>2.6367</v>
+        <v>2.7166</v>
       </c>
       <c r="G35">
         <v>2.4</v>
@@ -4276,37 +4276,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M35">
-        <v>0.6217338600000001</v>
+        <v>0.6405742800000001</v>
       </c>
       <c r="N35">
-        <v>-0.4694889620408166</v>
+        <v>-0.4883293820408166</v>
       </c>
       <c r="O35">
-        <v>-0.09389779240816332</v>
+        <v>-0.09766587640816332</v>
       </c>
       <c r="P35">
-        <v>-0.3755911696326533</v>
+        <v>-0.3906635056326532</v>
       </c>
       <c r="Q35">
-        <v>1.584408830367347</v>
+        <v>1.569336494367347</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1184680157309902</v>
+        <v>0.1195690462723689</v>
       </c>
       <c r="T35">
-        <v>1.494130887840927</v>
+        <v>1.516769234626396</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.04897429841095786</v>
+        <v>0.0475338778694591</v>
       </c>
       <c r="W35">
-        <v>0.2242518604346961</v>
+        <v>0.2245915115983816</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2448714920547893</v>
+        <v>0.2376693893472955</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4322,22 +4322,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1552766844832132</v>
+        <v>0.1571766844832131</v>
       </c>
       <c r="C36">
-        <v>2.845385107818303</v>
+        <v>2.724129237783198</v>
       </c>
       <c r="D36">
-        <v>3.161985107818304</v>
+        <v>3.120629237783198</v>
       </c>
       <c r="E36">
-        <v>-0.1833999999999998</v>
+        <v>-0.1034999999999995</v>
       </c>
       <c r="F36">
-        <v>2.7166</v>
+        <v>2.7965</v>
       </c>
       <c r="G36">
         <v>2.4</v>
@@ -4358,37 +4358,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M36">
-        <v>0.6405742800000001</v>
+        <v>0.6594147000000001</v>
       </c>
       <c r="N36">
-        <v>-0.4883293820408166</v>
+        <v>-0.5071698020408166</v>
       </c>
       <c r="O36">
-        <v>-0.09766587640816332</v>
+        <v>-0.1014339604081633</v>
       </c>
       <c r="P36">
-        <v>-0.3906635056326532</v>
+        <v>-0.4057358416326533</v>
       </c>
       <c r="Q36">
-        <v>1.569336494367347</v>
+        <v>1.554264158367347</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1195690462723689</v>
+        <v>0.1207039546765591</v>
       </c>
       <c r="T36">
-        <v>1.516769234626396</v>
+        <v>1.540104145928341</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.0475338778694591</v>
+        <v>0.04617576707318884</v>
       </c>
       <c r="W36">
-        <v>0.2245915115983816</v>
+        <v>0.2249117541241421</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2376693893472955</v>
+        <v>0.2308788353659442</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4404,22 +4404,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1571766844832131</v>
+        <v>0.1590766844832132</v>
       </c>
       <c r="C37">
-        <v>2.724129237783198</v>
+        <v>2.603941195368183</v>
       </c>
       <c r="D37">
-        <v>3.120629237783198</v>
+        <v>3.080341195368184</v>
       </c>
       <c r="E37">
-        <v>-0.1034999999999995</v>
+        <v>-0.02359999999999962</v>
       </c>
       <c r="F37">
-        <v>2.7965</v>
+        <v>2.8764</v>
       </c>
       <c r="G37">
         <v>2.4</v>
@@ -4440,37 +4440,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M37">
-        <v>0.6594147000000001</v>
+        <v>0.6782551200000001</v>
       </c>
       <c r="N37">
-        <v>-0.5071698020408166</v>
+        <v>-0.5260102220408166</v>
       </c>
       <c r="O37">
-        <v>-0.1014339604081633</v>
+        <v>-0.1052020444081633</v>
       </c>
       <c r="P37">
-        <v>-0.4057358416326533</v>
+        <v>-0.4208081776326533</v>
       </c>
       <c r="Q37">
-        <v>1.554264158367347</v>
+        <v>1.539191822367347</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1207039546765591</v>
+        <v>0.1218743289683804</v>
       </c>
       <c r="T37">
-        <v>1.540104145928341</v>
+        <v>1.564168273208471</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.04617576707318884</v>
+        <v>0.04489310687671137</v>
       </c>
       <c r="W37">
-        <v>0.2249117541241421</v>
+        <v>0.2252142053984715</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2308788353659442</v>
+        <v>0.2244655343835569</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4486,22 +4486,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1590766844832132</v>
+        <v>0.1609766844832132</v>
       </c>
       <c r="C38">
-        <v>2.603941195368183</v>
+        <v>2.484780150003552</v>
       </c>
       <c r="D38">
-        <v>3.080341195368184</v>
+        <v>3.041080150003553</v>
       </c>
       <c r="E38">
-        <v>-0.02360000000000007</v>
+        <v>0.05630000000000024</v>
       </c>
       <c r="F38">
-        <v>2.8764</v>
+        <v>2.9563</v>
       </c>
       <c r="G38">
         <v>2.4</v>
@@ -4522,37 +4522,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M38">
-        <v>0.67825512</v>
+        <v>0.6970955400000001</v>
       </c>
       <c r="N38">
-        <v>-0.5260102220408165</v>
+        <v>-0.5448506420408166</v>
       </c>
       <c r="O38">
-        <v>-0.1052020444081633</v>
+        <v>-0.1089701284081633</v>
       </c>
       <c r="P38">
-        <v>-0.4208081776326532</v>
+        <v>-0.4358805136326532</v>
       </c>
       <c r="Q38">
-        <v>1.539191822367347</v>
+        <v>1.524119486367347</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1218743289683804</v>
+        <v>0.1230818579996245</v>
       </c>
       <c r="T38">
-        <v>1.564168273208471</v>
+        <v>1.588996341037177</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.04489310687671138</v>
+        <v>0.04367977966382729</v>
       </c>
       <c r="W38">
-        <v>0.2252142053984715</v>
+        <v>0.2255003079552695</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2244655343835569</v>
+        <v>0.2183988983191364</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4568,22 +4568,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1609766844832132</v>
+        <v>0.1628766844832132</v>
       </c>
       <c r="C39">
-        <v>2.484780150003552</v>
+        <v>2.366607326575037</v>
       </c>
       <c r="D39">
-        <v>3.041080150003553</v>
+        <v>3.002807326575037</v>
       </c>
       <c r="E39">
-        <v>0.05630000000000024</v>
+        <v>0.1362000000000001</v>
       </c>
       <c r="F39">
-        <v>2.9563</v>
+        <v>3.0362</v>
       </c>
       <c r="G39">
         <v>2.4</v>
@@ -4604,37 +4604,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M39">
-        <v>0.6970955400000001</v>
+        <v>0.71593596</v>
       </c>
       <c r="N39">
-        <v>-0.5448506420408166</v>
+        <v>-0.5636910620408165</v>
       </c>
       <c r="O39">
-        <v>-0.1089701284081633</v>
+        <v>-0.1127382124081633</v>
       </c>
       <c r="P39">
-        <v>-0.4358805136326532</v>
+        <v>-0.4509528496326533</v>
       </c>
       <c r="Q39">
-        <v>1.524119486367347</v>
+        <v>1.509047150367347</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1230818579996245</v>
+        <v>0.1243283395802636</v>
       </c>
       <c r="T39">
-        <v>1.588996341037177</v>
+        <v>1.614625314279712</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.04367977966382729</v>
+        <v>0.04253031177793709</v>
       </c>
       <c r="W39">
-        <v>0.2255003079552695</v>
+        <v>0.2257713524827624</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2183988983191364</v>
+        <v>0.2126515588896855</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4650,22 +4650,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1628766844832132</v>
+        <v>0.1647766844832131</v>
       </c>
       <c r="C40">
-        <v>2.366607326575037</v>
+        <v>2.24938587768905</v>
       </c>
       <c r="D40">
-        <v>3.002807326575037</v>
+        <v>2.96548587768905</v>
       </c>
       <c r="E40">
-        <v>0.1362000000000001</v>
+        <v>0.2161000000000004</v>
       </c>
       <c r="F40">
-        <v>3.0362</v>
+        <v>3.1161</v>
       </c>
       <c r="G40">
         <v>2.4</v>
@@ -4686,37 +4686,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M40">
-        <v>0.71593596</v>
+        <v>0.7347763800000001</v>
       </c>
       <c r="N40">
-        <v>-0.5636910620408165</v>
+        <v>-0.5825314820408166</v>
       </c>
       <c r="O40">
-        <v>-0.1127382124081633</v>
+        <v>-0.1165062964081633</v>
       </c>
       <c r="P40">
-        <v>-0.4509528496326533</v>
+        <v>-0.4660251856326533</v>
       </c>
       <c r="Q40">
-        <v>1.509047150367347</v>
+        <v>1.493974814367347</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1243283395802636</v>
+        <v>0.1256156894094483</v>
       </c>
       <c r="T40">
-        <v>1.614625314279712</v>
+        <v>1.64109458172692</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.04253031177793709</v>
+        <v>0.04143979096311819</v>
       </c>
       <c r="W40">
-        <v>0.2257713524827624</v>
+        <v>0.2260284972908967</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2126515588896855</v>
+        <v>0.2071989548155909</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4732,22 +4732,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1647766844832131</v>
+        <v>0.1666766844832132</v>
       </c>
       <c r="C41">
-        <v>2.24938587768905</v>
+        <v>2.13308076534656</v>
       </c>
       <c r="D41">
-        <v>2.96548587768905</v>
+        <v>2.929080765346561</v>
       </c>
       <c r="E41">
-        <v>0.2161000000000004</v>
+        <v>0.2960000000000003</v>
       </c>
       <c r="F41">
-        <v>3.1161</v>
+        <v>3.196</v>
       </c>
       <c r="G41">
         <v>2.4</v>
@@ -4768,37 +4768,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M41">
-        <v>0.7347763800000001</v>
+        <v>0.7536168000000001</v>
       </c>
       <c r="N41">
-        <v>-0.5825314820408166</v>
+        <v>-0.6013719020408166</v>
       </c>
       <c r="O41">
-        <v>-0.1165062964081633</v>
+        <v>-0.1202743804081633</v>
       </c>
       <c r="P41">
-        <v>-0.4660251856326533</v>
+        <v>-0.4810975216326533</v>
       </c>
       <c r="Q41">
-        <v>1.493974814367347</v>
+        <v>1.478902478367347</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1256156894094483</v>
+        <v>0.1269459508996058</v>
       </c>
       <c r="T41">
-        <v>1.64109458172692</v>
+        <v>1.668446158089036</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.04143979096311819</v>
+        <v>0.04040379618904024</v>
       </c>
       <c r="W41">
-        <v>0.2260284972908967</v>
+        <v>0.2262727848586243</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2071989548155909</v>
+        <v>0.2020189809452012</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4814,22 +4814,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1666766844832132</v>
+        <v>0.1685766844832132</v>
       </c>
       <c r="C42">
-        <v>2.13308076534656</v>
+        <v>2.017658651226906</v>
       </c>
       <c r="D42">
-        <v>2.929080765346561</v>
+        <v>2.893558651226906</v>
       </c>
       <c r="E42">
-        <v>0.2960000000000003</v>
+        <v>0.3759000000000006</v>
       </c>
       <c r="F42">
-        <v>3.196</v>
+        <v>3.2759</v>
       </c>
       <c r="G42">
         <v>2.4</v>
@@ -4850,37 +4850,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M42">
-        <v>0.7536168000000001</v>
+        <v>0.7724572200000002</v>
       </c>
       <c r="N42">
-        <v>-0.6013719020408166</v>
+        <v>-0.6202123220408167</v>
       </c>
       <c r="O42">
-        <v>-0.1202743804081633</v>
+        <v>-0.1240424644081633</v>
       </c>
       <c r="P42">
-        <v>-0.4810975216326533</v>
+        <v>-0.4961698576326533</v>
       </c>
       <c r="Q42">
-        <v>1.478902478367347</v>
+        <v>1.463830142367347</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1269459508996058</v>
+        <v>0.128321305999599</v>
       </c>
       <c r="T42">
-        <v>1.668446158089036</v>
+        <v>1.696724906531223</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.04040379618904024</v>
+        <v>0.0394183377454051</v>
       </c>
       <c r="W42">
-        <v>0.2262727848586243</v>
+        <v>0.2265051559596335</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2020189809452012</v>
+        <v>0.1970916887270255</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4896,22 +4896,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1685766844832132</v>
+        <v>0.1704766844832132</v>
       </c>
       <c r="C43">
-        <v>2.017658651226906</v>
+        <v>1.903087794859356</v>
       </c>
       <c r="D43">
-        <v>2.893558651226906</v>
+        <v>2.858887794859357</v>
       </c>
       <c r="E43">
-        <v>0.3759000000000006</v>
+        <v>0.4558000000000004</v>
       </c>
       <c r="F43">
-        <v>3.2759</v>
+        <v>3.3558</v>
       </c>
       <c r="G43">
         <v>2.4</v>
@@ -4932,37 +4932,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M43">
-        <v>0.7724572200000002</v>
+        <v>0.7912976400000001</v>
       </c>
       <c r="N43">
-        <v>-0.6202123220408167</v>
+        <v>-0.6390527420408166</v>
       </c>
       <c r="O43">
-        <v>-0.1240424644081633</v>
+        <v>-0.1278105484081633</v>
       </c>
       <c r="P43">
-        <v>-0.4961698576326533</v>
+        <v>-0.5112421936326533</v>
       </c>
       <c r="Q43">
-        <v>1.463830142367347</v>
+        <v>1.448757806367347</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.128321305999599</v>
+        <v>0.1297440871375232</v>
       </c>
       <c r="T43">
-        <v>1.696724906531223</v>
+        <v>1.725978784230037</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.0394183377454051</v>
+        <v>0.03847980589432404</v>
       </c>
       <c r="W43">
-        <v>0.2265051559596335</v>
+        <v>0.2267264617701184</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1970916887270255</v>
+        <v>0.1923990294716201</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4978,22 +4978,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1704766844832132</v>
+        <v>0.1723766844832132</v>
       </c>
       <c r="C44">
-        <v>1.903087794859357</v>
+        <v>1.789337959028716</v>
       </c>
       <c r="D44">
-        <v>2.858887794859357</v>
+        <v>2.825037959028716</v>
       </c>
       <c r="E44">
-        <v>0.4558</v>
+        <v>0.5357000000000003</v>
       </c>
       <c r="F44">
-        <v>3.3558</v>
+        <v>3.4357</v>
       </c>
       <c r="G44">
         <v>2.4</v>
@@ -5014,37 +5014,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M44">
-        <v>0.79129764</v>
+        <v>0.8101380600000001</v>
       </c>
       <c r="N44">
-        <v>-0.6390527420408165</v>
+        <v>-0.6578931620408166</v>
       </c>
       <c r="O44">
-        <v>-0.1278105484081633</v>
+        <v>-0.1315786324081633</v>
       </c>
       <c r="P44">
-        <v>-0.5112421936326532</v>
+        <v>-0.5263145296326532</v>
       </c>
       <c r="Q44">
-        <v>1.448757806367347</v>
+        <v>1.433685470367347</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1297440871375232</v>
+        <v>0.1312167904206376</v>
       </c>
       <c r="T44">
-        <v>1.725978784230037</v>
+        <v>1.756259113777932</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03847980589432404</v>
+        <v>0.03758492668747929</v>
       </c>
       <c r="W44">
-        <v>0.2267264617701184</v>
+        <v>0.2269374742870924</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1923990294716201</v>
+        <v>0.1879246334373964</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5060,22 +5060,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1723766844832132</v>
+        <v>0.1742766844832132</v>
       </c>
       <c r="C45">
-        <v>1.789337959028716</v>
+        <v>1.676380321822386</v>
       </c>
       <c r="D45">
-        <v>2.825037959028716</v>
+        <v>2.791980321822386</v>
       </c>
       <c r="E45">
-        <v>0.5357000000000003</v>
+        <v>0.6156000000000001</v>
       </c>
       <c r="F45">
-        <v>3.4357</v>
+        <v>3.5156</v>
       </c>
       <c r="G45">
         <v>2.4</v>
@@ -5096,37 +5096,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M45">
-        <v>0.8101380600000001</v>
+        <v>0.8289784800000001</v>
       </c>
       <c r="N45">
-        <v>-0.6578931620408166</v>
+        <v>-0.6767335820408166</v>
       </c>
       <c r="O45">
-        <v>-0.1315786324081633</v>
+        <v>-0.1353467164081633</v>
       </c>
       <c r="P45">
-        <v>-0.5263145296326532</v>
+        <v>-0.5413868656326533</v>
       </c>
       <c r="Q45">
-        <v>1.433685470367347</v>
+        <v>1.418613134367347</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1312167904206376</v>
+        <v>0.1327420902495776</v>
       </c>
       <c r="T45">
-        <v>1.756259113777932</v>
+        <v>1.787620883666824</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.03758492668747929</v>
+        <v>0.03673072380821839</v>
       </c>
       <c r="W45">
-        <v>0.2269374742870924</v>
+        <v>0.2271388953260221</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1879246334373964</v>
+        <v>0.183653619041092</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5142,22 +5142,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1742766844832132</v>
+        <v>0.1761766844832132</v>
       </c>
       <c r="C46">
-        <v>1.676380321822386</v>
+        <v>1.564187394781178</v>
       </c>
       <c r="D46">
-        <v>2.791980321822386</v>
+        <v>2.759687394781178</v>
       </c>
       <c r="E46">
-        <v>0.6156000000000001</v>
+        <v>0.6955000000000005</v>
       </c>
       <c r="F46">
-        <v>3.5156</v>
+        <v>3.5955</v>
       </c>
       <c r="G46">
         <v>2.4</v>
@@ -5178,37 +5178,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M46">
-        <v>0.8289784800000001</v>
+        <v>0.8478189000000002</v>
       </c>
       <c r="N46">
-        <v>-0.6767335820408166</v>
+        <v>-0.6955740020408167</v>
       </c>
       <c r="O46">
-        <v>-0.1353467164081633</v>
+        <v>-0.1391148004081633</v>
       </c>
       <c r="P46">
-        <v>-0.5413868656326533</v>
+        <v>-0.5564592016326533</v>
       </c>
       <c r="Q46">
-        <v>1.418613134367347</v>
+        <v>1.403540798367347</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1327420902495776</v>
+        <v>0.1343228555268426</v>
       </c>
       <c r="T46">
-        <v>1.787620883666824</v>
+        <v>1.820123081551675</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.03673072380821839</v>
+        <v>0.0359144855013691</v>
       </c>
       <c r="W46">
-        <v>0.2271388953260221</v>
+        <v>0.2273313643187772</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.183653619041092</v>
+        <v>0.1795724275068454</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5224,22 +5224,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1761766844832132</v>
+        <v>0.1780766844832132</v>
       </c>
       <c r="C47">
-        <v>1.564187394781178</v>
+        <v>1.452732946665341</v>
       </c>
       <c r="D47">
-        <v>2.759687394781178</v>
+        <v>2.728132946665342</v>
       </c>
       <c r="E47">
-        <v>0.6955000000000005</v>
+        <v>0.7754000000000003</v>
       </c>
       <c r="F47">
-        <v>3.5955</v>
+        <v>3.6754</v>
       </c>
       <c r="G47">
         <v>2.4</v>
@@ -5260,37 +5260,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M47">
-        <v>0.8478189000000002</v>
+        <v>0.8666593200000001</v>
       </c>
       <c r="N47">
-        <v>-0.6955740020408167</v>
+        <v>-0.7144144220408166</v>
       </c>
       <c r="O47">
-        <v>-0.1391148004081633</v>
+        <v>-0.1428828844081633</v>
       </c>
       <c r="P47">
-        <v>-0.5564592016326533</v>
+        <v>-0.5715315376326533</v>
       </c>
       <c r="Q47">
-        <v>1.403540798367347</v>
+        <v>1.388468462367347</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1343228555268426</v>
+        <v>0.1359621676662286</v>
       </c>
       <c r="T47">
-        <v>1.820123081551675</v>
+        <v>1.853829064543373</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.0359144855013691</v>
+        <v>0.03513373581655673</v>
       </c>
       <c r="W47">
-        <v>0.2273313643187772</v>
+        <v>0.2275154650944559</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1795724275068454</v>
+        <v>0.1756686790827836</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5306,22 +5306,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1780766844832132</v>
+        <v>0.1799766844832132</v>
       </c>
       <c r="C48">
-        <v>1.452732946665341</v>
+        <v>1.341991932391454</v>
       </c>
       <c r="D48">
-        <v>2.728132946665342</v>
+        <v>2.697291932391455</v>
       </c>
       <c r="E48">
-        <v>0.7754000000000003</v>
+        <v>0.8553000000000006</v>
       </c>
       <c r="F48">
-        <v>3.6754</v>
+        <v>3.755300000000001</v>
       </c>
       <c r="G48">
         <v>2.4</v>
@@ -5342,37 +5342,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M48">
-        <v>0.8666593200000001</v>
+        <v>0.8854997400000002</v>
       </c>
       <c r="N48">
-        <v>-0.7144144220408166</v>
+        <v>-0.7332548420408167</v>
       </c>
       <c r="O48">
-        <v>-0.1428828844081633</v>
+        <v>-0.1466509684081634</v>
       </c>
       <c r="P48">
-        <v>-0.5715315376326533</v>
+        <v>-0.5866038736326533</v>
       </c>
       <c r="Q48">
-        <v>1.388468462367347</v>
+        <v>1.373396126367347</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1359621676662286</v>
+        <v>0.1376633406410631</v>
       </c>
       <c r="T48">
-        <v>1.853829064543373</v>
+        <v>1.88880697142155</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.03513373581655673</v>
+        <v>0.03438620952258743</v>
       </c>
       <c r="W48">
-        <v>0.2275154650944559</v>
+        <v>0.2276917317945739</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1756686790827836</v>
+        <v>0.1719310476129371</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5388,22 +5388,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1799766844832132</v>
+        <v>0.1818766844832131</v>
       </c>
       <c r="C49">
-        <v>1.341991932391454</v>
+        <v>1.23194042673556</v>
       </c>
       <c r="D49">
-        <v>2.697291932391455</v>
+        <v>2.667140426735561</v>
       </c>
       <c r="E49">
-        <v>0.8553000000000006</v>
+        <v>0.9352000000000005</v>
       </c>
       <c r="F49">
-        <v>3.755300000000001</v>
+        <v>3.8352</v>
       </c>
       <c r="G49">
         <v>2.4</v>
@@ -5424,37 +5424,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M49">
-        <v>0.8854997400000002</v>
+        <v>0.9043401600000002</v>
       </c>
       <c r="N49">
-        <v>-0.7332548420408167</v>
+        <v>-0.7520952620408167</v>
       </c>
       <c r="O49">
-        <v>-0.1466509684081634</v>
+        <v>-0.1504190524081633</v>
       </c>
       <c r="P49">
-        <v>-0.5866038736326533</v>
+        <v>-0.6016762096326533</v>
       </c>
       <c r="Q49">
-        <v>1.373396126367347</v>
+        <v>1.358323790367347</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1376633406410631</v>
+        <v>0.1394299433456989</v>
       </c>
       <c r="T49">
-        <v>1.88880697142155</v>
+        <v>1.925130182410426</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.03438620952258743</v>
+        <v>0.03366983015753353</v>
       </c>
       <c r="W49">
-        <v>0.2276917317945739</v>
+        <v>0.2278606540488536</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1719310476129371</v>
+        <v>0.1683491507876677</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5470,22 +5470,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1818766844832131</v>
+        <v>0.1837766844832132</v>
       </c>
       <c r="C50">
-        <v>1.231940426735561</v>
+        <v>1.122555562433718</v>
       </c>
       <c r="D50">
-        <v>2.667140426735561</v>
+        <v>2.637655562433718</v>
       </c>
       <c r="E50">
-        <v>0.9352</v>
+        <v>1.0151</v>
       </c>
       <c r="F50">
-        <v>3.8352</v>
+        <v>3.9151</v>
       </c>
       <c r="G50">
         <v>2.4</v>
@@ -5506,37 +5506,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M50">
-        <v>0.9043401600000001</v>
+        <v>0.9231805800000001</v>
       </c>
       <c r="N50">
-        <v>-0.7520952620408166</v>
+        <v>-0.7709356820408166</v>
       </c>
       <c r="O50">
-        <v>-0.1504190524081633</v>
+        <v>-0.1541871364081633</v>
       </c>
       <c r="P50">
-        <v>-0.6016762096326532</v>
+        <v>-0.6167485456326534</v>
       </c>
       <c r="Q50">
-        <v>1.358323790367347</v>
+        <v>1.343251454367347</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1394299433456989</v>
+        <v>0.1412658245877715</v>
       </c>
       <c r="T50">
-        <v>1.925130182410425</v>
+        <v>1.962877833045924</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.03366983015753353</v>
+        <v>0.03298269076656345</v>
       </c>
       <c r="W50">
-        <v>0.2278606540488536</v>
+        <v>0.2280226815172443</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1683491507876677</v>
+        <v>0.1649134538328173</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5552,22 +5552,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1837766844832132</v>
+        <v>0.1856766844832132</v>
       </c>
       <c r="C51">
-        <v>1.122555562433718</v>
+        <v>1.013815472343395</v>
       </c>
       <c r="D51">
-        <v>2.637655562433718</v>
+        <v>2.608815472343395</v>
       </c>
       <c r="E51">
-        <v>1.0151</v>
+        <v>1.095</v>
       </c>
       <c r="F51">
-        <v>3.9151</v>
+        <v>3.995</v>
       </c>
       <c r="G51">
         <v>2.4</v>
@@ -5588,37 +5588,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M51">
-        <v>0.9231805800000001</v>
+        <v>0.9420210000000001</v>
       </c>
       <c r="N51">
-        <v>-0.7709356820408166</v>
+        <v>-0.7897761020408166</v>
       </c>
       <c r="O51">
-        <v>-0.1541871364081633</v>
+        <v>-0.1579552204081633</v>
       </c>
       <c r="P51">
-        <v>-0.6167485456326534</v>
+        <v>-0.6318208816326533</v>
       </c>
       <c r="Q51">
-        <v>1.343251454367347</v>
+        <v>1.328179118367347</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1412658245877715</v>
+        <v>0.1431751410795269</v>
       </c>
       <c r="T51">
-        <v>1.962877833045924</v>
+        <v>2.002135389706843</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.03298269076656345</v>
+        <v>0.03232303695123219</v>
       </c>
       <c r="W51">
-        <v>0.2280226815172443</v>
+        <v>0.2281782278868995</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1649134538328173</v>
+        <v>0.161615184756161</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5634,22 +5634,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1856766844832132</v>
+        <v>0.1875766844832132</v>
       </c>
       <c r="C52">
-        <v>1.013815472343395</v>
+        <v>0.9056992353582745</v>
       </c>
       <c r="D52">
-        <v>2.608815472343395</v>
+        <v>2.580599235358275</v>
       </c>
       <c r="E52">
-        <v>1.095</v>
+        <v>1.1749</v>
       </c>
       <c r="F52">
-        <v>3.995</v>
+        <v>4.0749</v>
       </c>
       <c r="G52">
         <v>2.4</v>
@@ -5670,37 +5670,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M52">
-        <v>0.9420210000000001</v>
+        <v>0.9608614200000002</v>
       </c>
       <c r="N52">
-        <v>-0.7897761020408166</v>
+        <v>-0.8086165220408167</v>
       </c>
       <c r="O52">
-        <v>-0.1579552204081633</v>
+        <v>-0.1617233044081633</v>
       </c>
       <c r="P52">
-        <v>-0.6318208816326533</v>
+        <v>-0.6468932176326534</v>
       </c>
       <c r="Q52">
-        <v>1.328179118367347</v>
+        <v>1.313106782367347</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1431751410795269</v>
+        <v>0.1451623888566601</v>
       </c>
       <c r="T52">
-        <v>2.002135389706843</v>
+        <v>2.042995295619227</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.03232303695123219</v>
+        <v>0.03168925191297273</v>
       </c>
       <c r="W52">
-        <v>0.2281782278868995</v>
+        <v>0.228327674398921</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.161615184756161</v>
+        <v>0.1584462595648637</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5716,22 +5716,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1875766844832132</v>
+        <v>0.1894766844832131</v>
       </c>
       <c r="C53">
-        <v>0.9056992353582745</v>
+        <v>0.798186825795316</v>
       </c>
       <c r="D53">
-        <v>2.580599235358275</v>
+        <v>2.552986825795316</v>
       </c>
       <c r="E53">
-        <v>1.1749</v>
+        <v>1.2548</v>
       </c>
       <c r="F53">
-        <v>4.0749</v>
+        <v>4.1548</v>
       </c>
       <c r="G53">
         <v>2.4</v>
@@ -5752,37 +5752,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M53">
-        <v>0.9608614200000002</v>
+        <v>0.97970184</v>
       </c>
       <c r="N53">
-        <v>-0.8086165220408167</v>
+        <v>-0.8274569420408165</v>
       </c>
       <c r="O53">
-        <v>-0.1617233044081633</v>
+        <v>-0.1654913884081633</v>
       </c>
       <c r="P53">
-        <v>-0.6468932176326534</v>
+        <v>-0.6619655536326532</v>
       </c>
       <c r="Q53">
-        <v>1.313106782367347</v>
+        <v>1.298034446367347</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1451623888566601</v>
+        <v>0.1472324386245072</v>
       </c>
       <c r="T53">
-        <v>2.042995295619227</v>
+        <v>2.085557697611295</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03168925191297273</v>
+        <v>0.03107984322233864</v>
       </c>
       <c r="W53">
-        <v>0.228327674398921</v>
+        <v>0.2284713729681725</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1584462595648637</v>
+        <v>0.1553992161116933</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5798,22 +5798,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1894766844832131</v>
+        <v>0.1913766844832132</v>
       </c>
       <c r="C54">
-        <v>0.798186825795316</v>
+        <v>0.6912590659967695</v>
       </c>
       <c r="D54">
-        <v>2.552986825795316</v>
+        <v>2.52595906599677</v>
       </c>
       <c r="E54">
-        <v>1.2548</v>
+        <v>1.3347</v>
       </c>
       <c r="F54">
-        <v>4.1548</v>
+        <v>4.2347</v>
       </c>
       <c r="G54">
         <v>2.4</v>
@@ -5834,37 +5834,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M54">
-        <v>0.97970184</v>
+        <v>0.9985422600000001</v>
       </c>
       <c r="N54">
-        <v>-0.8274569420408165</v>
+        <v>-0.8462973620408166</v>
       </c>
       <c r="O54">
-        <v>-0.1654913884081633</v>
+        <v>-0.1692594724081633</v>
       </c>
       <c r="P54">
-        <v>-0.6619655536326532</v>
+        <v>-0.6770378896326533</v>
       </c>
       <c r="Q54">
-        <v>1.298034446367347</v>
+        <v>1.282962110367347</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1472324386245072</v>
+        <v>0.149390575616518</v>
       </c>
       <c r="T54">
-        <v>2.085557697611295</v>
+        <v>2.129931265645578</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03107984322233864</v>
+        <v>0.0304934310860681</v>
       </c>
       <c r="W54">
-        <v>0.2284713729681725</v>
+        <v>0.2286096489499052</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1553992161116933</v>
+        <v>0.1524671554303405</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5880,22 +5880,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1913766844832132</v>
+        <v>0.1932766844832132</v>
       </c>
       <c r="C55">
-        <v>0.6912590659967695</v>
+        <v>0.584897581911398</v>
       </c>
       <c r="D55">
-        <v>2.52595906599677</v>
+        <v>2.499497581911398</v>
       </c>
       <c r="E55">
-        <v>1.3347</v>
+        <v>1.414600000000001</v>
       </c>
       <c r="F55">
-        <v>4.2347</v>
+        <v>4.3146</v>
       </c>
       <c r="G55">
         <v>2.4</v>
@@ -5916,37 +5916,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M55">
-        <v>0.9985422600000001</v>
+        <v>1.01738268</v>
       </c>
       <c r="N55">
-        <v>-0.8462973620408166</v>
+        <v>-0.8651377820408166</v>
       </c>
       <c r="O55">
-        <v>-0.1692594724081633</v>
+        <v>-0.1730275564081633</v>
       </c>
       <c r="P55">
-        <v>-0.6770378896326533</v>
+        <v>-0.6921102256326532</v>
       </c>
       <c r="Q55">
-        <v>1.282962110367347</v>
+        <v>1.267889774367347</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.149390575616518</v>
+        <v>0.1516425446516597</v>
       </c>
       <c r="T55">
-        <v>2.129931265645578</v>
+        <v>2.176234119246569</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.0304934310860681</v>
+        <v>0.02992873791780758</v>
       </c>
       <c r="W55">
-        <v>0.2286096489499052</v>
+        <v>0.228742803598981</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1524671554303405</v>
+        <v>0.149643689589038</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5962,22 +5962,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1932766844832132</v>
+        <v>0.1951766844832132</v>
       </c>
       <c r="C56">
-        <v>0.584897581911398</v>
+        <v>0.4790847614386724</v>
       </c>
       <c r="D56">
-        <v>2.499497581911398</v>
+        <v>2.473584761438673</v>
       </c>
       <c r="E56">
-        <v>1.414600000000001</v>
+        <v>1.494500000000001</v>
       </c>
       <c r="F56">
-        <v>4.3146</v>
+        <v>4.394500000000001</v>
       </c>
       <c r="G56">
         <v>2.4</v>
@@ -5998,37 +5998,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M56">
-        <v>1.01738268</v>
+        <v>1.0362231</v>
       </c>
       <c r="N56">
-        <v>-0.8651377820408166</v>
+        <v>-0.8839782020408167</v>
       </c>
       <c r="O56">
-        <v>-0.1730275564081633</v>
+        <v>-0.1767956404081633</v>
       </c>
       <c r="P56">
-        <v>-0.6921102256326532</v>
+        <v>-0.7071825616326534</v>
       </c>
       <c r="Q56">
-        <v>1.267889774367347</v>
+        <v>1.252817438367347</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1516425446516597</v>
+        <v>0.1539946011994743</v>
       </c>
       <c r="T56">
-        <v>2.176234119246569</v>
+        <v>2.224594877452048</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02992873791780758</v>
+        <v>0.02938457904657472</v>
       </c>
       <c r="W56">
-        <v>0.228742803598981</v>
+        <v>0.2288711162608177</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.149643689589038</v>
+        <v>0.1469228952328736</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6044,22 +6044,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1951766844832132</v>
+        <v>0.1970766844832132</v>
       </c>
       <c r="C57">
-        <v>0.4790847614386724</v>
+        <v>0.3738037153375258</v>
       </c>
       <c r="D57">
-        <v>2.473584761438673</v>
+        <v>2.448203715337526</v>
       </c>
       <c r="E57">
-        <v>1.494500000000001</v>
+        <v>1.5744</v>
       </c>
       <c r="F57">
-        <v>4.394500000000001</v>
+        <v>4.4744</v>
       </c>
       <c r="G57">
         <v>2.4</v>
@@ -6080,37 +6080,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M57">
-        <v>1.0362231</v>
+        <v>1.05506352</v>
       </c>
       <c r="N57">
-        <v>-0.8839782020408167</v>
+        <v>-0.9028186220408165</v>
       </c>
       <c r="O57">
-        <v>-0.1767956404081633</v>
+        <v>-0.1805637244081633</v>
       </c>
       <c r="P57">
-        <v>-0.7071825616326534</v>
+        <v>-0.7222548976326533</v>
       </c>
       <c r="Q57">
-        <v>1.252817438367347</v>
+        <v>1.237745102367347</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1539946011994743</v>
+        <v>0.1564535694085533</v>
       </c>
       <c r="T57">
-        <v>2.224594877452048</v>
+        <v>2.275153851939594</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02938457904657472</v>
+        <v>0.02885985442074303</v>
       </c>
       <c r="W57">
-        <v>0.2288711162608177</v>
+        <v>0.2289948463275888</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1469228952328736</v>
+        <v>0.1442992721037152</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6126,22 +6126,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1970766844832132</v>
+        <v>0.1989766844832132</v>
       </c>
       <c r="C58">
-        <v>0.3738037153375258</v>
+        <v>0.2690382405173004</v>
       </c>
       <c r="D58">
-        <v>2.448203715337526</v>
+        <v>2.423338240517301</v>
       </c>
       <c r="E58">
-        <v>1.5744</v>
+        <v>1.654300000000001</v>
       </c>
       <c r="F58">
-        <v>4.4744</v>
+        <v>4.5543</v>
       </c>
       <c r="G58">
         <v>2.4</v>
@@ -6162,37 +6162,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M58">
-        <v>1.05506352</v>
+        <v>1.07390394</v>
       </c>
       <c r="N58">
-        <v>-0.9028186220408165</v>
+        <v>-0.9216590420408166</v>
       </c>
       <c r="O58">
-        <v>-0.1805637244081633</v>
+        <v>-0.1843318084081633</v>
       </c>
       <c r="P58">
-        <v>-0.7222548976326533</v>
+        <v>-0.7373272336326533</v>
       </c>
       <c r="Q58">
-        <v>1.237745102367347</v>
+        <v>1.222672766367347</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1564535694085533</v>
+        <v>0.159026908232008</v>
       </c>
       <c r="T58">
-        <v>2.275153851939594</v>
+        <v>2.328064406635864</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02885985442074303</v>
+        <v>0.02835354118529139</v>
       </c>
       <c r="W58">
-        <v>0.2289948463275888</v>
+        <v>0.2291142349885083</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1442992721037152</v>
+        <v>0.1417677059264569</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6208,22 +6208,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1989766844832132</v>
+        <v>0.2008766844832132</v>
       </c>
       <c r="C59">
-        <v>0.2690382405173004</v>
+        <v>0.1647727855432626</v>
       </c>
       <c r="D59">
-        <v>2.423338240517301</v>
+        <v>2.398972785543263</v>
       </c>
       <c r="E59">
-        <v>1.654300000000001</v>
+        <v>1.734200000000001</v>
       </c>
       <c r="F59">
-        <v>4.5543</v>
+        <v>4.634200000000001</v>
       </c>
       <c r="G59">
         <v>2.4</v>
@@ -6244,37 +6244,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M59">
-        <v>1.07390394</v>
+        <v>1.09274436</v>
       </c>
       <c r="N59">
-        <v>-0.9216590420408166</v>
+        <v>-0.9404994620408167</v>
       </c>
       <c r="O59">
-        <v>-0.1843318084081633</v>
+        <v>-0.1880998924081634</v>
       </c>
       <c r="P59">
-        <v>-0.7373272336326533</v>
+        <v>-0.7523995696326533</v>
       </c>
       <c r="Q59">
-        <v>1.222672766367347</v>
+        <v>1.207600430367347</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.159026908232008</v>
+        <v>0.1617227869994368</v>
       </c>
       <c r="T59">
-        <v>2.328064406635864</v>
+        <v>2.383494511555766</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02835354118529139</v>
+        <v>0.0278646870269243</v>
       </c>
       <c r="W59">
-        <v>0.2291142349885083</v>
+        <v>0.2292295067990512</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1417677059264569</v>
+        <v>0.1393234351346215</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6290,22 +6290,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2008766844832132</v>
+        <v>0.2027766844832131</v>
       </c>
       <c r="C60">
-        <v>0.1647727855432635</v>
+        <v>0.06099241820232848</v>
       </c>
       <c r="D60">
-        <v>2.398972785543263</v>
+        <v>2.375092418202329</v>
       </c>
       <c r="E60">
-        <v>1.7342</v>
+        <v>1.8141</v>
       </c>
       <c r="F60">
-        <v>4.6342</v>
+        <v>4.7141</v>
       </c>
       <c r="G60">
         <v>2.4</v>
@@ -6326,37 +6326,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M60">
-        <v>1.09274436</v>
+        <v>1.11158478</v>
       </c>
       <c r="N60">
-        <v>-0.9404994620408165</v>
+        <v>-0.9593398820408165</v>
       </c>
       <c r="O60">
-        <v>-0.1880998924081633</v>
+        <v>-0.1918679764081633</v>
       </c>
       <c r="P60">
-        <v>-0.7523995696326532</v>
+        <v>-0.7674719056326532</v>
       </c>
       <c r="Q60">
-        <v>1.207600430367347</v>
+        <v>1.192528094367347</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1617227869994368</v>
+        <v>0.1645501720482035</v>
       </c>
       <c r="T60">
-        <v>2.383494511555765</v>
+        <v>2.441628524032735</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02786468702692431</v>
+        <v>0.02739240419595949</v>
       </c>
       <c r="W60">
-        <v>0.2292295067990512</v>
+        <v>0.2293408710905928</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1393234351346215</v>
+        <v>0.1369620209797974</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6372,22 +6372,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2027766844832131</v>
+        <v>0.2046766844832132</v>
       </c>
       <c r="C61">
-        <v>0.06099241820232848</v>
+        <v>-0.0423172050131031</v>
       </c>
       <c r="D61">
-        <v>2.375092418202329</v>
+        <v>2.351682794986896</v>
       </c>
       <c r="E61">
-        <v>1.8141</v>
+        <v>1.894</v>
       </c>
       <c r="F61">
-        <v>4.7141</v>
+        <v>4.794</v>
       </c>
       <c r="G61">
         <v>2.4</v>
@@ -6408,37 +6408,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M61">
-        <v>1.11158478</v>
+        <v>1.1304252</v>
       </c>
       <c r="N61">
-        <v>-0.9593398820408165</v>
+        <v>-0.9781803020408164</v>
       </c>
       <c r="O61">
-        <v>-0.1918679764081633</v>
+        <v>-0.1956360604081633</v>
       </c>
       <c r="P61">
-        <v>-0.7674719056326532</v>
+        <v>-0.7825442416326531</v>
       </c>
       <c r="Q61">
-        <v>1.192528094367347</v>
+        <v>1.177455758367347</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1645501720482035</v>
+        <v>0.1675189263494086</v>
       </c>
       <c r="T61">
-        <v>2.441628524032735</v>
+        <v>2.502669237133553</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02739240419595949</v>
+        <v>0.02693586412602683</v>
       </c>
       <c r="W61">
-        <v>0.2293408710905928</v>
+        <v>0.2294485232390829</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1369620209797974</v>
+        <v>0.1346793206301341</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6454,22 +6454,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2046766844832132</v>
+        <v>0.2065766844832131</v>
       </c>
       <c r="C62">
-        <v>-0.0423172050131031</v>
+        <v>-0.1451698676342765</v>
       </c>
       <c r="D62">
-        <v>2.351682794986896</v>
+        <v>2.328730132365723</v>
       </c>
       <c r="E62">
-        <v>1.894</v>
+        <v>1.9739</v>
       </c>
       <c r="F62">
-        <v>4.794</v>
+        <v>4.8739</v>
       </c>
       <c r="G62">
         <v>2.4</v>
@@ -6490,37 +6490,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M62">
-        <v>1.1304252</v>
+        <v>1.14926562</v>
       </c>
       <c r="N62">
-        <v>-0.9781803020408164</v>
+        <v>-0.9970207220408165</v>
       </c>
       <c r="O62">
-        <v>-0.1956360604081633</v>
+        <v>-0.1994041444081633</v>
       </c>
       <c r="P62">
-        <v>-0.7825442416326531</v>
+        <v>-0.7976165776326531</v>
       </c>
       <c r="Q62">
-        <v>1.177455758367347</v>
+        <v>1.162383422367347</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1675189263494086</v>
+        <v>0.1706399244609319</v>
       </c>
       <c r="T62">
-        <v>2.502669237133553</v>
+        <v>2.566840243213901</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.02693586412602683</v>
+        <v>0.02649429258297721</v>
       </c>
       <c r="W62">
-        <v>0.2294485232390829</v>
+        <v>0.229552645808934</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1346793206301341</v>
+        <v>0.132471462914886</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6536,22 +6536,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2065766844832131</v>
+        <v>0.2084766844832132</v>
       </c>
       <c r="C63">
-        <v>-0.1451698676342765</v>
+        <v>-0.2475788202790721</v>
       </c>
       <c r="D63">
-        <v>2.328730132365723</v>
+        <v>2.306221179720928</v>
       </c>
       <c r="E63">
-        <v>1.9739</v>
+        <v>2.0538</v>
       </c>
       <c r="F63">
-        <v>4.8739</v>
+        <v>4.9538</v>
       </c>
       <c r="G63">
         <v>2.4</v>
@@ -6572,37 +6572,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M63">
-        <v>1.14926562</v>
+        <v>1.16810604</v>
       </c>
       <c r="N63">
-        <v>-0.9970207220408165</v>
+        <v>-1.015861142040817</v>
       </c>
       <c r="O63">
-        <v>-0.1994041444081633</v>
+        <v>-0.2031722284081633</v>
       </c>
       <c r="P63">
-        <v>-0.7976165776326531</v>
+        <v>-0.8126889136326533</v>
       </c>
       <c r="Q63">
-        <v>1.162383422367347</v>
+        <v>1.147311086367347</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1706399244609319</v>
+        <v>0.1739251856309564</v>
       </c>
       <c r="T63">
-        <v>2.566840243213901</v>
+        <v>2.634388670666898</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02649429258297721</v>
+        <v>0.02606696528325177</v>
       </c>
       <c r="W63">
-        <v>0.229552645808934</v>
+        <v>0.2296534095862092</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.132471462914886</v>
+        <v>0.1303348264162588</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6618,22 +6618,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2084766844832132</v>
+        <v>0.2103766844832132</v>
       </c>
       <c r="C64">
-        <v>-0.2475788202790721</v>
+        <v>-0.3495568061605168</v>
       </c>
       <c r="D64">
-        <v>2.306221179720928</v>
+        <v>2.284143193839484</v>
       </c>
       <c r="E64">
-        <v>2.0538</v>
+        <v>2.133700000000001</v>
       </c>
       <c r="F64">
-        <v>4.9538</v>
+        <v>5.033700000000001</v>
       </c>
       <c r="G64">
         <v>2.4</v>
@@ -6654,37 +6654,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M64">
-        <v>1.16810604</v>
+        <v>1.18694646</v>
       </c>
       <c r="N64">
-        <v>-1.015861142040817</v>
+        <v>-1.034701562040817</v>
       </c>
       <c r="O64">
-        <v>-0.2031722284081633</v>
+        <v>-0.2069403124081634</v>
       </c>
       <c r="P64">
-        <v>-0.8126889136326533</v>
+        <v>-0.8277612496326533</v>
       </c>
       <c r="Q64">
-        <v>1.147311086367347</v>
+        <v>1.132238750367347</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1739251856309564</v>
+        <v>0.1773880284858471</v>
       </c>
       <c r="T64">
-        <v>2.634388670666898</v>
+        <v>2.705588364468706</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02606696528325177</v>
+        <v>0.02565320392954936</v>
       </c>
       <c r="W64">
-        <v>0.2296534095862092</v>
+        <v>0.2297509745134123</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1303348264162588</v>
+        <v>0.1282660196477468</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6700,22 +6700,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2103766844832132</v>
+        <v>0.2122766844832132</v>
       </c>
       <c r="C65">
-        <v>-0.3495568061605168</v>
+        <v>-0.4511160851439948</v>
       </c>
       <c r="D65">
-        <v>2.284143193839484</v>
+        <v>2.262483914856005</v>
       </c>
       <c r="E65">
-        <v>2.133700000000001</v>
+        <v>2.2136</v>
       </c>
       <c r="F65">
-        <v>5.033700000000001</v>
+        <v>5.1136</v>
       </c>
       <c r="G65">
         <v>2.4</v>
@@ -6736,37 +6736,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M65">
-        <v>1.18694646</v>
+        <v>1.20578688</v>
       </c>
       <c r="N65">
-        <v>-1.034701562040817</v>
+        <v>-1.053541982040817</v>
       </c>
       <c r="O65">
-        <v>-0.2069403124081634</v>
+        <v>-0.2107083964081633</v>
       </c>
       <c r="P65">
-        <v>-0.8277612496326533</v>
+        <v>-0.8428335856326532</v>
       </c>
       <c r="Q65">
-        <v>1.132238750367347</v>
+        <v>1.117166414367347</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1773880284858471</v>
+        <v>0.1810432514993429</v>
       </c>
       <c r="T65">
-        <v>2.705588364468706</v>
+        <v>2.780743596815059</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02565320392954936</v>
+        <v>0.02525237261815015</v>
       </c>
       <c r="W65">
-        <v>0.2297509745134123</v>
+        <v>0.2298454905366402</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1282660196477468</v>
+        <v>0.1262618630907507</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6782,22 +6782,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2122766844832132</v>
+        <v>0.2141766844832132</v>
       </c>
       <c r="C66">
-        <v>-0.4511160851439948</v>
+        <v>-0.5522684564485969</v>
       </c>
       <c r="D66">
-        <v>2.262483914856005</v>
+        <v>2.241231543551403</v>
       </c>
       <c r="E66">
-        <v>2.2136</v>
+        <v>2.2935</v>
       </c>
       <c r="F66">
-        <v>5.1136</v>
+        <v>5.1935</v>
       </c>
       <c r="G66">
         <v>2.4</v>
@@ -6818,37 +6818,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M66">
-        <v>1.20578688</v>
+        <v>1.2246273</v>
       </c>
       <c r="N66">
-        <v>-1.053541982040817</v>
+        <v>-1.072382402040817</v>
       </c>
       <c r="O66">
-        <v>-0.2107083964081633</v>
+        <v>-0.2144764804081633</v>
       </c>
       <c r="P66">
-        <v>-0.8428335856326532</v>
+        <v>-0.8579059216326532</v>
       </c>
       <c r="Q66">
-        <v>1.117166414367347</v>
+        <v>1.102094078367347</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1810432514993429</v>
+        <v>0.1849073443993242</v>
       </c>
       <c r="T66">
-        <v>2.780743596815059</v>
+        <v>2.860193413866919</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02525237261815015</v>
+        <v>0.02486387457787092</v>
       </c>
       <c r="W66">
-        <v>0.2298454905366402</v>
+        <v>0.229937098374538</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1262618630907507</v>
+        <v>0.1243193728893546</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6864,22 +6864,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2141766844832132</v>
+        <v>0.2160766844832132</v>
       </c>
       <c r="C67">
-        <v>-0.5522684564485969</v>
+        <v>-0.6530252800808984</v>
       </c>
       <c r="D67">
-        <v>2.241231543551403</v>
+        <v>2.220374719919103</v>
       </c>
       <c r="E67">
-        <v>2.2935</v>
+        <v>2.373400000000001</v>
       </c>
       <c r="F67">
-        <v>5.1935</v>
+        <v>5.273400000000001</v>
       </c>
       <c r="G67">
         <v>2.4</v>
@@ -6900,37 +6900,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M67">
-        <v>1.2246273</v>
+        <v>1.24346772</v>
       </c>
       <c r="N67">
-        <v>-1.072382402040817</v>
+        <v>-1.091222822040817</v>
       </c>
       <c r="O67">
-        <v>-0.2144764804081633</v>
+        <v>-0.2182445644081633</v>
       </c>
       <c r="P67">
-        <v>-0.8579059216326532</v>
+        <v>-0.8729782576326534</v>
       </c>
       <c r="Q67">
-        <v>1.102094078367347</v>
+        <v>1.087021742367347</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1849073443993242</v>
+        <v>0.1889987368816572</v>
       </c>
       <c r="T67">
-        <v>2.860193413866919</v>
+        <v>2.944316749568887</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02486387457787092</v>
+        <v>0.02448714920547893</v>
       </c>
       <c r="W67">
-        <v>0.229937098374538</v>
+        <v>0.2300259302173481</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1243193728893546</v>
+        <v>0.1224357460273946</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6946,22 +6946,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2160766844832132</v>
+        <v>0.2179766844832132</v>
       </c>
       <c r="C68">
-        <v>-0.6530252800808984</v>
+        <v>-0.7533974970830268</v>
       </c>
       <c r="D68">
-        <v>2.220374719919103</v>
+        <v>2.199902502916975</v>
       </c>
       <c r="E68">
-        <v>2.373400000000001</v>
+        <v>2.453300000000001</v>
       </c>
       <c r="F68">
-        <v>5.273400000000001</v>
+        <v>5.353300000000001</v>
       </c>
       <c r="G68">
         <v>2.4</v>
@@ -6982,37 +6982,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M68">
-        <v>1.24346772</v>
+        <v>1.26230814</v>
       </c>
       <c r="N68">
-        <v>-1.091222822040817</v>
+        <v>-1.110063242040817</v>
       </c>
       <c r="O68">
-        <v>-0.2182445644081633</v>
+        <v>-0.2220126484081634</v>
       </c>
       <c r="P68">
-        <v>-0.8729782576326534</v>
+        <v>-0.8880505936326534</v>
       </c>
       <c r="Q68">
-        <v>1.087021742367347</v>
+        <v>1.071949406367346</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1889987368816572</v>
+        <v>0.1933380925447377</v>
       </c>
       <c r="T68">
-        <v>2.944316749568887</v>
+        <v>3.033538469252792</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02448714920547893</v>
+        <v>0.02412166936659119</v>
       </c>
       <c r="W68">
-        <v>0.2300259302173481</v>
+        <v>0.2301121103633578</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1224357460273946</v>
+        <v>0.120608346832956</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7028,22 +7028,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2179766844832132</v>
+        <v>0.2198766844832132</v>
       </c>
       <c r="C69">
-        <v>-0.7533974970830268</v>
+        <v>-0.8533956486707988</v>
       </c>
       <c r="D69">
-        <v>2.199902502916975</v>
+        <v>2.179804351329202</v>
       </c>
       <c r="E69">
-        <v>2.453300000000001</v>
+        <v>2.5332</v>
       </c>
       <c r="F69">
-        <v>5.353300000000001</v>
+        <v>5.4332</v>
       </c>
       <c r="G69">
         <v>2.4</v>
@@ -7064,37 +7064,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M69">
-        <v>1.26230814</v>
+        <v>1.28114856</v>
       </c>
       <c r="N69">
-        <v>-1.110063242040817</v>
+        <v>-1.128903662040817</v>
       </c>
       <c r="O69">
-        <v>-0.2220126484081634</v>
+        <v>-0.2257807324081633</v>
       </c>
       <c r="P69">
-        <v>-0.8880505936326534</v>
+        <v>-0.9031229296326533</v>
       </c>
       <c r="Q69">
-        <v>1.071949406367346</v>
+        <v>1.056877070367347</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1933380925447377</v>
+        <v>0.1979486579367608</v>
       </c>
       <c r="T69">
-        <v>3.033538469252792</v>
+        <v>3.128336546416942</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02412166936659119</v>
+        <v>0.02376693893472955</v>
       </c>
       <c r="W69">
-        <v>0.2301121103633578</v>
+        <v>0.2301957557991908</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.120608346832956</v>
+        <v>0.1188346946736477</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7110,22 +7110,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2198766844832132</v>
+        <v>0.2217766844832132</v>
       </c>
       <c r="C70">
-        <v>-0.8533956486707988</v>
+        <v>-0.9530298943323059</v>
       </c>
       <c r="D70">
-        <v>2.179804351329202</v>
+        <v>2.160070105667695</v>
       </c>
       <c r="E70">
-        <v>2.5332</v>
+        <v>2.613100000000001</v>
       </c>
       <c r="F70">
-        <v>5.4332</v>
+        <v>5.513100000000001</v>
       </c>
       <c r="G70">
         <v>2.4</v>
@@ -7146,37 +7146,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M70">
-        <v>1.28114856</v>
+        <v>1.29998898</v>
       </c>
       <c r="N70">
-        <v>-1.128903662040817</v>
+        <v>-1.147744082040817</v>
       </c>
       <c r="O70">
-        <v>-0.2257807324081633</v>
+        <v>-0.2295488164081634</v>
       </c>
       <c r="P70">
-        <v>-0.9031229296326533</v>
+        <v>-0.9181952656326533</v>
       </c>
       <c r="Q70">
-        <v>1.056877070367347</v>
+        <v>1.041804734367347</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1979486579367608</v>
+        <v>0.2028566791605273</v>
       </c>
       <c r="T70">
-        <v>3.128336546416942</v>
+        <v>3.229250628559424</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02376693893472955</v>
+        <v>0.02342249054437115</v>
       </c>
       <c r="W70">
-        <v>0.2301957557991908</v>
+        <v>0.2302769767296373</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1188346946736477</v>
+        <v>0.1171124527218558</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2217766844832132</v>
+        <v>0.2236766844832132</v>
       </c>
       <c r="C71">
-        <v>-0.9530298943323059</v>
+        <v>-1.052310028952196</v>
       </c>
       <c r="D71">
-        <v>2.160070105667695</v>
+        <v>2.140689971047805</v>
       </c>
       <c r="E71">
-        <v>2.613100000000001</v>
+        <v>2.693000000000001</v>
       </c>
       <c r="F71">
-        <v>5.513100000000001</v>
+        <v>5.593000000000001</v>
       </c>
       <c r="G71">
         <v>2.4</v>
@@ -7228,37 +7228,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M71">
-        <v>1.29998898</v>
+        <v>1.3188294</v>
       </c>
       <c r="N71">
-        <v>-1.147744082040817</v>
+        <v>-1.166584502040817</v>
       </c>
       <c r="O71">
-        <v>-0.2295488164081634</v>
+        <v>-0.2333169004081634</v>
       </c>
       <c r="P71">
-        <v>-0.9181952656326533</v>
+        <v>-0.9332676016326534</v>
       </c>
       <c r="Q71">
-        <v>1.041804734367347</v>
+        <v>1.026732398367347</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2028566791605273</v>
+        <v>0.2080919017992115</v>
       </c>
       <c r="T71">
-        <v>3.229250628559424</v>
+        <v>3.336892316178072</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02342249054437115</v>
+        <v>0.02308788353659442</v>
       </c>
       <c r="W71">
-        <v>0.2302769767296373</v>
+        <v>0.2303558770620711</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1171124527218558</v>
+        <v>0.1154394176829721</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7274,22 +7274,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2236766844832132</v>
+        <v>0.2255766844832132</v>
       </c>
       <c r="C72">
-        <v>-1.052310028952196</v>
+        <v>-1.151245499022336</v>
       </c>
       <c r="D72">
-        <v>2.140689971047805</v>
+        <v>2.121654500977666</v>
       </c>
       <c r="E72">
-        <v>2.693000000000001</v>
+        <v>2.772900000000001</v>
       </c>
       <c r="F72">
-        <v>5.593000000000001</v>
+        <v>5.672900000000001</v>
       </c>
       <c r="G72">
         <v>2.4</v>
@@ -7310,37 +7310,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M72">
-        <v>1.3188294</v>
+        <v>1.33766982</v>
       </c>
       <c r="N72">
-        <v>-1.166584502040817</v>
+        <v>-1.185424922040817</v>
       </c>
       <c r="O72">
-        <v>-0.2333169004081634</v>
+        <v>-0.2370849844081634</v>
       </c>
       <c r="P72">
-        <v>-0.9332676016326534</v>
+        <v>-0.9483399376326535</v>
       </c>
       <c r="Q72">
-        <v>1.026732398367347</v>
+        <v>1.011660062367346</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2080919017992115</v>
+        <v>0.2136881742750464</v>
       </c>
       <c r="T72">
-        <v>3.336892316178072</v>
+        <v>3.451957568460075</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02308788353659442</v>
+        <v>0.02276270207833252</v>
       </c>
       <c r="W72">
-        <v>0.2303558770620711</v>
+        <v>0.2304325548499292</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1154394176829721</v>
+        <v>0.1138135103916627</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7356,22 +7356,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2255766844832132</v>
+        <v>0.2274766844832132</v>
       </c>
       <c r="C73">
-        <v>-1.151245499022335</v>
+        <v>-1.249845417995198</v>
       </c>
       <c r="D73">
-        <v>2.121654500977666</v>
+        <v>2.102954582004802</v>
       </c>
       <c r="E73">
-        <v>2.7729</v>
+        <v>2.8528</v>
       </c>
       <c r="F73">
-        <v>5.6729</v>
+        <v>5.7528</v>
       </c>
       <c r="G73">
         <v>2.4</v>
@@ -7392,37 +7392,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M73">
-        <v>1.33766982</v>
+        <v>1.35651024</v>
       </c>
       <c r="N73">
-        <v>-1.185424922040817</v>
+        <v>-1.204265342040816</v>
       </c>
       <c r="O73">
-        <v>-0.2370849844081633</v>
+        <v>-0.2408530684081633</v>
       </c>
       <c r="P73">
-        <v>-0.9483399376326533</v>
+        <v>-0.9634122736326531</v>
       </c>
       <c r="Q73">
-        <v>1.011660062367347</v>
+        <v>0.9965877263673468</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2136881742750463</v>
+        <v>0.2196841804991551</v>
       </c>
       <c r="T73">
-        <v>3.451957568460073</v>
+        <v>3.575241767333647</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02276270207833253</v>
+        <v>0.02244655343835569</v>
       </c>
       <c r="W73">
-        <v>0.2304325548499292</v>
+        <v>0.2305071026992357</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1138135103916627</v>
+        <v>0.1122327671917784</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7438,22 +7438,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2274766844832132</v>
+        <v>0.2293766844832132</v>
       </c>
       <c r="C74">
-        <v>-1.249845417995198</v>
+        <v>-1.348118580832414</v>
       </c>
       <c r="D74">
-        <v>2.102954582004802</v>
+        <v>2.084581419167587</v>
       </c>
       <c r="E74">
-        <v>2.8528</v>
+        <v>2.9327</v>
       </c>
       <c r="F74">
-        <v>5.7528</v>
+        <v>5.8327</v>
       </c>
       <c r="G74">
         <v>2.4</v>
@@ -7474,37 +7474,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M74">
-        <v>1.35651024</v>
+        <v>1.37535066</v>
       </c>
       <c r="N74">
-        <v>-1.204265342040816</v>
+        <v>-1.223105762040817</v>
       </c>
       <c r="O74">
-        <v>-0.2408530684081633</v>
+        <v>-0.2446211524081633</v>
       </c>
       <c r="P74">
-        <v>-0.9634122736326531</v>
+        <v>-0.9784846096326533</v>
       </c>
       <c r="Q74">
-        <v>0.9965877263673468</v>
+        <v>0.9815153903673467</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2196841804991551</v>
+        <v>0.2261243353324572</v>
       </c>
       <c r="T74">
-        <v>3.575241767333647</v>
+        <v>3.707658129086746</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02244655343835569</v>
+        <v>0.02213906640495356</v>
       </c>
       <c r="W74">
-        <v>0.2305071026992357</v>
+        <v>0.230579608141712</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1122327671917784</v>
+        <v>0.1106953320247678</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7520,22 +7520,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2293766844832132</v>
+        <v>0.2312766844832132</v>
       </c>
       <c r="C75">
-        <v>-1.348118580832414</v>
+        <v>-1.446073477797261</v>
       </c>
       <c r="D75">
-        <v>2.084581419167587</v>
+        <v>2.066526522202739</v>
       </c>
       <c r="E75">
-        <v>2.9327</v>
+        <v>3.0126</v>
       </c>
       <c r="F75">
-        <v>5.8327</v>
+        <v>5.9126</v>
       </c>
       <c r="G75">
         <v>2.4</v>
@@ -7556,37 +7556,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M75">
-        <v>1.37535066</v>
+        <v>1.39419108</v>
       </c>
       <c r="N75">
-        <v>-1.223105762040817</v>
+        <v>-1.241946182040817</v>
       </c>
       <c r="O75">
-        <v>-0.2446211524081633</v>
+        <v>-0.2483892364081633</v>
       </c>
       <c r="P75">
-        <v>-0.9784846096326533</v>
+        <v>-0.9935569456326533</v>
       </c>
       <c r="Q75">
-        <v>0.9815153903673467</v>
+        <v>0.9664430543673467</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2261243353324572</v>
+        <v>0.2330598866913978</v>
       </c>
       <c r="T75">
-        <v>3.707658129086746</v>
+        <v>3.850260364820851</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02213906640495356</v>
+        <v>0.02183988983191364</v>
       </c>
       <c r="W75">
-        <v>0.230579608141712</v>
+        <v>0.2306501539776348</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1106953320247678</v>
+        <v>0.1091994491595683</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7602,22 +7602,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2312766844832132</v>
+        <v>0.2331766844832132</v>
       </c>
       <c r="C76">
-        <v>-1.446073477797261</v>
+        <v>-1.543718307536588</v>
       </c>
       <c r="D76">
-        <v>2.066526522202739</v>
+        <v>2.048781692463411</v>
       </c>
       <c r="E76">
-        <v>3.0126</v>
+        <v>3.0925</v>
       </c>
       <c r="F76">
-        <v>5.9126</v>
+        <v>5.9925</v>
       </c>
       <c r="G76">
         <v>2.4</v>
@@ -7638,37 +7638,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M76">
-        <v>1.39419108</v>
+        <v>1.4130315</v>
       </c>
       <c r="N76">
-        <v>-1.241946182040817</v>
+        <v>-1.260786602040816</v>
       </c>
       <c r="O76">
-        <v>-0.2483892364081633</v>
+        <v>-0.2521573204081633</v>
       </c>
       <c r="P76">
-        <v>-0.9935569456326533</v>
+        <v>-1.008629281632653</v>
       </c>
       <c r="Q76">
-        <v>0.9664430543673467</v>
+        <v>0.9513707183673468</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2330598866913978</v>
+        <v>0.2405502821590538</v>
       </c>
       <c r="T76">
-        <v>3.850260364820851</v>
+        <v>4.004270779413686</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02183988983191364</v>
+        <v>0.02154869130082146</v>
       </c>
       <c r="W76">
-        <v>0.2306501539776348</v>
+        <v>0.2307188185912663</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1091994491595683</v>
+        <v>0.1077434565041073</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7684,22 +7684,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2331766844832132</v>
+        <v>0.2350766844832132</v>
       </c>
       <c r="C77">
-        <v>-1.543718307536588</v>
+        <v>-1.641060989494454</v>
       </c>
       <c r="D77">
-        <v>2.048781692463411</v>
+        <v>2.031339010505546</v>
       </c>
       <c r="E77">
-        <v>3.0925</v>
+        <v>3.1724</v>
       </c>
       <c r="F77">
-        <v>5.9925</v>
+        <v>6.0724</v>
       </c>
       <c r="G77">
         <v>2.4</v>
@@ -7720,37 +7720,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M77">
-        <v>1.4130315</v>
+        <v>1.43187192</v>
       </c>
       <c r="N77">
-        <v>-1.260786602040816</v>
+        <v>-1.279627022040817</v>
       </c>
       <c r="O77">
-        <v>-0.2521573204081633</v>
+        <v>-0.2559254044081633</v>
       </c>
       <c r="P77">
-        <v>-1.008629281632653</v>
+        <v>-1.023701617632653</v>
       </c>
       <c r="Q77">
-        <v>0.9513707183673468</v>
+        <v>0.9362983823673467</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2405502821590538</v>
+        <v>0.2486648772490143</v>
       </c>
       <c r="T77">
-        <v>4.004270779413686</v>
+        <v>4.171115395222589</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02154869130082146</v>
+        <v>0.02126515588896855</v>
       </c>
       <c r="W77">
-        <v>0.2307188185912663</v>
+        <v>0.2307856762413812</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1077434565041073</v>
+        <v>0.1063257794448428</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7766,22 +7766,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2350766844832132</v>
+        <v>0.2369766844832132</v>
       </c>
       <c r="C78">
-        <v>-1.641060989494454</v>
+        <v>-1.738109175697019</v>
       </c>
       <c r="D78">
-        <v>2.031339010505546</v>
+        <v>2.014190824302982</v>
       </c>
       <c r="E78">
-        <v>3.1724</v>
+        <v>3.2523</v>
       </c>
       <c r="F78">
-        <v>6.0724</v>
+        <v>6.1523</v>
       </c>
       <c r="G78">
         <v>2.4</v>
@@ -7802,37 +7802,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M78">
-        <v>1.43187192</v>
+        <v>1.45071234</v>
       </c>
       <c r="N78">
-        <v>-1.279627022040817</v>
+        <v>-1.298467442040817</v>
       </c>
       <c r="O78">
-        <v>-0.2559254044081633</v>
+        <v>-0.2596934884081634</v>
       </c>
       <c r="P78">
-        <v>-1.023701617632653</v>
+        <v>-1.038773953632653</v>
       </c>
       <c r="Q78">
-        <v>0.9362983823673467</v>
+        <v>0.9212260463673467</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2486648772490143</v>
+        <v>0.2574850893033194</v>
       </c>
       <c r="T78">
-        <v>4.171115395222589</v>
+        <v>4.352468238493137</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02126515588896855</v>
+        <v>0.02098898503326765</v>
       </c>
       <c r="W78">
-        <v>0.2307856762413812</v>
+        <v>0.2308507973291555</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1063257794448428</v>
+        <v>0.1049449251663382</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7848,22 +7848,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2369766844832132</v>
+        <v>0.2388766844832132</v>
       </c>
       <c r="C79">
-        <v>-1.738109175697019</v>
+        <v>-1.834870261945519</v>
       </c>
       <c r="D79">
-        <v>2.014190824302982</v>
+        <v>1.997329738054481</v>
       </c>
       <c r="E79">
-        <v>3.2523</v>
+        <v>3.332200000000001</v>
       </c>
       <c r="F79">
-        <v>6.1523</v>
+        <v>6.232200000000001</v>
       </c>
       <c r="G79">
         <v>2.4</v>
@@ -7884,37 +7884,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M79">
-        <v>1.45071234</v>
+        <v>1.46955276</v>
       </c>
       <c r="N79">
-        <v>-1.298467442040817</v>
+        <v>-1.317307862040817</v>
       </c>
       <c r="O79">
-        <v>-0.2596934884081634</v>
+        <v>-0.2634615724081634</v>
       </c>
       <c r="P79">
-        <v>-1.038773953632653</v>
+        <v>-1.053846289632653</v>
       </c>
       <c r="Q79">
-        <v>0.9212260463673467</v>
+        <v>0.9061537103673465</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2574850893033194</v>
+        <v>0.2671071388171065</v>
       </c>
       <c r="T79">
-        <v>4.352468238493137</v>
+        <v>4.550307703879188</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02098898503326765</v>
+        <v>0.0207198954815591</v>
       </c>
       <c r="W79">
-        <v>0.2308507973291555</v>
+        <v>0.2309142486454484</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1049449251663382</v>
+        <v>0.1035994774077955</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7930,22 +7930,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2388766844832132</v>
+        <v>0.2407766844832132</v>
       </c>
       <c r="C80">
-        <v>-1.834870261945519</v>
+        <v>-1.931351398451718</v>
       </c>
       <c r="D80">
-        <v>1.997329738054481</v>
+        <v>1.980748601548282</v>
       </c>
       <c r="E80">
-        <v>3.332200000000001</v>
+        <v>3.4121</v>
       </c>
       <c r="F80">
-        <v>6.232200000000001</v>
+        <v>6.3121</v>
       </c>
       <c r="G80">
         <v>2.4</v>
@@ -7966,37 +7966,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M80">
-        <v>1.46955276</v>
+        <v>1.48839318</v>
       </c>
       <c r="N80">
-        <v>-1.317307862040817</v>
+        <v>-1.336148282040817</v>
       </c>
       <c r="O80">
-        <v>-0.2634615724081634</v>
+        <v>-0.2672296564081633</v>
       </c>
       <c r="P80">
-        <v>-1.053846289632653</v>
+        <v>-1.068918625632653</v>
       </c>
       <c r="Q80">
-        <v>0.9061537103673465</v>
+        <v>0.8910813743673467</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2671071388171065</v>
+        <v>0.2776455739988736</v>
       </c>
       <c r="T80">
-        <v>4.550307703879188</v>
+        <v>4.766989023111532</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0207198954815591</v>
+        <v>0.02045761832356468</v>
       </c>
       <c r="W80">
-        <v>0.2309142486454484</v>
+        <v>0.2309760935993035</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1035994774077955</v>
+        <v>0.1022880916178234</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8012,22 +8012,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2407766844832132</v>
+        <v>0.2426766844832132</v>
       </c>
       <c r="C81">
-        <v>-1.931351398451718</v>
+        <v>-2.027559499947967</v>
       </c>
       <c r="D81">
-        <v>1.980748601548282</v>
+        <v>1.964440500052034</v>
       </c>
       <c r="E81">
-        <v>3.4121</v>
+        <v>3.492</v>
       </c>
       <c r="F81">
-        <v>6.3121</v>
+        <v>6.392</v>
       </c>
       <c r="G81">
         <v>2.4</v>
@@ -8048,37 +8048,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M81">
-        <v>1.48839318</v>
+        <v>1.5072336</v>
       </c>
       <c r="N81">
-        <v>-1.336148282040817</v>
+        <v>-1.354988702040817</v>
       </c>
       <c r="O81">
-        <v>-0.2672296564081633</v>
+        <v>-0.2709977404081633</v>
       </c>
       <c r="P81">
-        <v>-1.068918625632653</v>
+        <v>-1.083990961632653</v>
       </c>
       <c r="Q81">
-        <v>0.8910813743673467</v>
+        <v>0.8760090383673467</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2776455739988736</v>
+        <v>0.2892378526988172</v>
       </c>
       <c r="T81">
-        <v>4.766989023111532</v>
+        <v>5.005338474267108</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02045761832356468</v>
+        <v>0.02020189809452012</v>
       </c>
       <c r="W81">
-        <v>0.2309760935993035</v>
+        <v>0.2310363924293122</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1022880916178234</v>
+        <v>0.1010094904726005</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8094,22 +8094,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2426766844832132</v>
+        <v>0.2445766844832132</v>
       </c>
       <c r="C82">
-        <v>-2.027559499947967</v>
+        <v>-2.123501255301909</v>
       </c>
       <c r="D82">
-        <v>1.964440500052034</v>
+        <v>1.948398744698091</v>
       </c>
       <c r="E82">
-        <v>3.492</v>
+        <v>3.571900000000001</v>
       </c>
       <c r="F82">
-        <v>6.392</v>
+        <v>6.471900000000001</v>
       </c>
       <c r="G82">
         <v>2.4</v>
@@ -8130,37 +8130,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M82">
-        <v>1.5072336</v>
+        <v>1.52607402</v>
       </c>
       <c r="N82">
-        <v>-1.354988702040817</v>
+        <v>-1.373829122040817</v>
       </c>
       <c r="O82">
-        <v>-0.2709977404081633</v>
+        <v>-0.2747658244081634</v>
       </c>
       <c r="P82">
-        <v>-1.083990961632653</v>
+        <v>-1.099063297632653</v>
       </c>
       <c r="Q82">
-        <v>0.8760090383673467</v>
+        <v>0.8609367023673467</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2892378526988172</v>
+        <v>0.3020503712619129</v>
       </c>
       <c r="T82">
-        <v>5.005338474267108</v>
+        <v>5.268777341333799</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02020189809452012</v>
+        <v>0.01995249194520506</v>
       </c>
       <c r="W82">
-        <v>0.2310363924293122</v>
+        <v>0.2310952023993207</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1010094904726005</v>
+        <v>0.09976245972602527</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8176,22 +8176,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2445766844832132</v>
+        <v>0.2464766844832132</v>
       </c>
       <c r="C83">
-        <v>-2.123501255301909</v>
+        <v>-2.219183136663916</v>
       </c>
       <c r="D83">
-        <v>1.948398744698091</v>
+        <v>1.932616863336085</v>
       </c>
       <c r="E83">
-        <v>3.571900000000001</v>
+        <v>3.651800000000001</v>
       </c>
       <c r="F83">
-        <v>6.471900000000001</v>
+        <v>6.551800000000001</v>
       </c>
       <c r="G83">
         <v>2.4</v>
@@ -8212,37 +8212,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M83">
-        <v>1.52607402</v>
+        <v>1.54491444</v>
       </c>
       <c r="N83">
-        <v>-1.373829122040817</v>
+        <v>-1.392669542040817</v>
       </c>
       <c r="O83">
-        <v>-0.2747658244081634</v>
+        <v>-0.2785339084081634</v>
       </c>
       <c r="P83">
-        <v>-1.099063297632653</v>
+        <v>-1.114135633632654</v>
       </c>
       <c r="Q83">
-        <v>0.8609367023673467</v>
+        <v>0.8458643663673464</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3020503712619129</v>
+        <v>0.3162865029986858</v>
       </c>
       <c r="T83">
-        <v>5.268777341333799</v>
+        <v>5.56148719363012</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01995249194520506</v>
+        <v>0.01970916887270255</v>
       </c>
       <c r="W83">
-        <v>0.2310952023993207</v>
+        <v>0.2311525779798168</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.09976245972602527</v>
+        <v>0.09854584436351277</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8258,22 +8258,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2464766844832132</v>
+        <v>0.2483766844832132</v>
       </c>
       <c r="C84">
-        <v>-2.219183136663916</v>
+        <v>-2.314611408173527</v>
       </c>
       <c r="D84">
-        <v>1.932616863336085</v>
+        <v>1.917088591826473</v>
       </c>
       <c r="E84">
-        <v>3.651800000000001</v>
+        <v>3.7317</v>
       </c>
       <c r="F84">
-        <v>6.551800000000001</v>
+        <v>6.6317</v>
       </c>
       <c r="G84">
         <v>2.4</v>
@@ -8294,37 +8294,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M84">
-        <v>1.54491444</v>
+        <v>1.56375486</v>
       </c>
       <c r="N84">
-        <v>-1.392669542040817</v>
+        <v>-1.411509962040817</v>
       </c>
       <c r="O84">
-        <v>-0.2785339084081634</v>
+        <v>-0.2823019924081633</v>
       </c>
       <c r="P84">
-        <v>-1.114135633632654</v>
+        <v>-1.129207969632653</v>
       </c>
       <c r="Q84">
-        <v>0.8458643663673464</v>
+        <v>0.8307920303673466</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3162865029986858</v>
+        <v>0.3321974737633144</v>
       </c>
       <c r="T84">
-        <v>5.56148719363012</v>
+        <v>5.888633499137774</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01970916887270255</v>
+        <v>0.01947170900676638</v>
       </c>
       <c r="W84">
-        <v>0.2311525779798168</v>
+        <v>0.2312085710162045</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.09854584436351277</v>
+        <v>0.0973585450338319</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8340,22 +8340,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2483766844832132</v>
+        <v>0.2502766844832132</v>
       </c>
       <c r="C85">
-        <v>-2.314611408173527</v>
+        <v>-2.409792134249525</v>
       </c>
       <c r="D85">
-        <v>1.917088591826473</v>
+        <v>1.901807865750476</v>
       </c>
       <c r="E85">
-        <v>3.7317</v>
+        <v>3.811600000000001</v>
       </c>
       <c r="F85">
-        <v>6.6317</v>
+        <v>6.711600000000001</v>
       </c>
       <c r="G85">
         <v>2.4</v>
@@ -8376,37 +8376,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M85">
-        <v>1.56375486</v>
+        <v>1.58259528</v>
       </c>
       <c r="N85">
-        <v>-1.411509962040817</v>
+        <v>-1.430350382040817</v>
       </c>
       <c r="O85">
-        <v>-0.2823019924081633</v>
+        <v>-0.2860700764081633</v>
       </c>
       <c r="P85">
-        <v>-1.129207969632653</v>
+        <v>-1.144280305632653</v>
       </c>
       <c r="Q85">
-        <v>0.8307920303673466</v>
+        <v>0.8157196943673466</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3321974737633144</v>
+        <v>0.3500973158735217</v>
       </c>
       <c r="T85">
-        <v>5.888633499137774</v>
+        <v>6.256673092833887</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01947170900676638</v>
+        <v>0.01923990294716202</v>
       </c>
       <c r="W85">
-        <v>0.2312085710162045</v>
+        <v>0.2312632308850592</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.0973585450338319</v>
+        <v>0.09619951473581012</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8422,22 +8422,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2502766844832132</v>
+        <v>0.2521766844832132</v>
       </c>
       <c r="C86">
-        <v>-2.409792134249523</v>
+        <v>-2.504731187486642</v>
       </c>
       <c r="D86">
-        <v>1.901807865750477</v>
+        <v>1.886768812513359</v>
       </c>
       <c r="E86">
-        <v>3.8116</v>
+        <v>3.8915</v>
       </c>
       <c r="F86">
-        <v>6.7116</v>
+        <v>6.7915</v>
       </c>
       <c r="G86">
         <v>2.4</v>
@@ -8458,37 +8458,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M86">
-        <v>1.58259528</v>
+        <v>1.6014357</v>
       </c>
       <c r="N86">
-        <v>-1.430350382040817</v>
+        <v>-1.449190802040817</v>
       </c>
       <c r="O86">
-        <v>-0.2860700764081633</v>
+        <v>-0.2898381604081633</v>
       </c>
       <c r="P86">
-        <v>-1.144280305632653</v>
+        <v>-1.159352641632653</v>
       </c>
       <c r="Q86">
-        <v>0.8157196943673468</v>
+        <v>0.8006473583673466</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3500973158735215</v>
+        <v>0.3703838035984229</v>
       </c>
       <c r="T86">
-        <v>6.256673092833883</v>
+        <v>6.673784632356142</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01923990294716202</v>
+        <v>0.01901355114778364</v>
       </c>
       <c r="W86">
-        <v>0.2312632308850592</v>
+        <v>0.2313166046393526</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.09619951473581012</v>
+        <v>0.09506775573891824</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8504,22 +8504,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2521766844832132</v>
+        <v>0.2540766844832132</v>
       </c>
       <c r="C87">
-        <v>-2.504731187486642</v>
+        <v>-2.599434256180573</v>
       </c>
       <c r="D87">
-        <v>1.886768812513359</v>
+        <v>1.871965743819428</v>
       </c>
       <c r="E87">
-        <v>3.8915</v>
+        <v>3.9714</v>
       </c>
       <c r="F87">
-        <v>6.7915</v>
+        <v>6.8714</v>
       </c>
       <c r="G87">
         <v>2.4</v>
@@ -8540,37 +8540,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M87">
-        <v>1.6014357</v>
+        <v>1.62027612</v>
       </c>
       <c r="N87">
-        <v>-1.449190802040817</v>
+        <v>-1.468031222040817</v>
       </c>
       <c r="O87">
-        <v>-0.2898381604081633</v>
+        <v>-0.2936062444081634</v>
       </c>
       <c r="P87">
-        <v>-1.159352641632653</v>
+        <v>-1.174424977632653</v>
       </c>
       <c r="Q87">
-        <v>0.8006473583673466</v>
+        <v>0.7855750223673466</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3703838035984229</v>
+        <v>0.3935683609983103</v>
       </c>
       <c r="T87">
-        <v>6.673784632356142</v>
+        <v>7.150483534667295</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01901355114778364</v>
+        <v>0.01879246334373964</v>
       </c>
       <c r="W87">
-        <v>0.2313166046393526</v>
+        <v>0.2313687371435462</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.09506775573891824</v>
+        <v>0.09396231671869826</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8586,22 +8586,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2540766844832132</v>
+        <v>0.2559766844832132</v>
       </c>
       <c r="C88">
-        <v>-2.599434256180573</v>
+        <v>-2.693906851501476</v>
       </c>
       <c r="D88">
-        <v>1.871965743819428</v>
+        <v>1.857393148498524</v>
       </c>
       <c r="E88">
-        <v>3.9714</v>
+        <v>4.051299999999999</v>
       </c>
       <c r="F88">
-        <v>6.8714</v>
+        <v>6.9513</v>
       </c>
       <c r="G88">
         <v>2.4</v>
@@ -8622,37 +8622,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M88">
-        <v>1.62027612</v>
+        <v>1.63911654</v>
       </c>
       <c r="N88">
-        <v>-1.468031222040817</v>
+        <v>-1.486871642040817</v>
       </c>
       <c r="O88">
-        <v>-0.2936062444081634</v>
+        <v>-0.2973743284081633</v>
       </c>
       <c r="P88">
-        <v>-1.174424977632653</v>
+        <v>-1.189497313632653</v>
       </c>
       <c r="Q88">
-        <v>0.7855750223673466</v>
+        <v>0.7705026863673468</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3935683609983103</v>
+        <v>0.4203197733827957</v>
       </c>
       <c r="T88">
-        <v>7.150483534667295</v>
+        <v>7.700520729641703</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01879246334373964</v>
+        <v>0.01857645801794953</v>
       </c>
       <c r="W88">
-        <v>0.2313687371435462</v>
+        <v>0.2314196711993675</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.09396231671869826</v>
+        <v>0.09288229008974769</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8668,22 +8668,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2559766844832132</v>
+        <v>0.2578766844832132</v>
       </c>
       <c r="C89">
-        <v>-2.693906851501476</v>
+        <v>-2.78815431433503</v>
       </c>
       <c r="D89">
-        <v>1.857393148498524</v>
+        <v>1.843045685664971</v>
       </c>
       <c r="E89">
-        <v>4.051299999999999</v>
+        <v>4.1312</v>
       </c>
       <c r="F89">
-        <v>6.9513</v>
+        <v>7.0312</v>
       </c>
       <c r="G89">
         <v>2.4</v>
@@ -8704,37 +8704,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M89">
-        <v>1.63911654</v>
+        <v>1.65795696</v>
       </c>
       <c r="N89">
-        <v>-1.486871642040817</v>
+        <v>-1.505712062040817</v>
       </c>
       <c r="O89">
-        <v>-0.2973743284081633</v>
+        <v>-0.3011424124081634</v>
       </c>
       <c r="P89">
-        <v>-1.189497313632653</v>
+        <v>-1.204569649632653</v>
       </c>
       <c r="Q89">
-        <v>0.7705026863673468</v>
+        <v>0.7554303503673467</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4203197733827957</v>
+        <v>0.4515297544980287</v>
       </c>
       <c r="T89">
-        <v>7.700520729641703</v>
+        <v>8.342230790445178</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01857645801794953</v>
+        <v>0.0183653619041092</v>
       </c>
       <c r="W89">
-        <v>0.2314196711993675</v>
+        <v>0.2314694476630111</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.09288229008974769</v>
+        <v>0.091826809520546</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8750,22 +8750,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2578766844832132</v>
+        <v>0.2597766844832132</v>
       </c>
       <c r="C90">
-        <v>-2.78815431433503</v>
+        <v>-2.882181821808834</v>
       </c>
       <c r="D90">
-        <v>1.843045685664971</v>
+        <v>1.828918178191167</v>
       </c>
       <c r="E90">
-        <v>4.1312</v>
+        <v>4.2111</v>
       </c>
       <c r="F90">
-        <v>7.0312</v>
+        <v>7.1111</v>
       </c>
       <c r="G90">
         <v>2.4</v>
@@ -8786,37 +8786,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M90">
-        <v>1.65795696</v>
+        <v>1.67679738</v>
       </c>
       <c r="N90">
-        <v>-1.505712062040817</v>
+        <v>-1.524552482040817</v>
       </c>
       <c r="O90">
-        <v>-0.3011424124081634</v>
+        <v>-0.3049104964081634</v>
       </c>
       <c r="P90">
-        <v>-1.204569649632653</v>
+        <v>-1.219641985632653</v>
       </c>
       <c r="Q90">
-        <v>0.7554303503673467</v>
+        <v>0.7403580143673465</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4515297544980287</v>
+        <v>0.4884142776342131</v>
       </c>
       <c r="T90">
-        <v>8.342230790445178</v>
+        <v>9.100615407758376</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0183653619041092</v>
+        <v>0.01815900952316415</v>
       </c>
       <c r="W90">
-        <v>0.2314694476630111</v>
+        <v>0.2315181055544379</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.091826809520546</v>
+        <v>0.0907950476158208</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8832,22 +8832,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2597766844832132</v>
+        <v>0.2616766844832131</v>
       </c>
       <c r="C91">
-        <v>-2.882181821808834</v>
+        <v>-2.975994393520955</v>
       </c>
       <c r="D91">
-        <v>1.828918178191167</v>
+        <v>1.815005606479045</v>
       </c>
       <c r="E91">
-        <v>4.2111</v>
+        <v>4.291</v>
       </c>
       <c r="F91">
-        <v>7.1111</v>
+        <v>7.191000000000001</v>
       </c>
       <c r="G91">
         <v>2.4</v>
@@ -8868,37 +8868,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M91">
-        <v>1.67679738</v>
+        <v>1.6956378</v>
       </c>
       <c r="N91">
-        <v>-1.524552482040817</v>
+        <v>-1.543392902040817</v>
       </c>
       <c r="O91">
-        <v>-0.3049104964081634</v>
+        <v>-0.3086785804081634</v>
       </c>
       <c r="P91">
-        <v>-1.219641985632653</v>
+        <v>-1.234714321632653</v>
       </c>
       <c r="Q91">
-        <v>0.7403580143673465</v>
+        <v>0.7252856783673465</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4884142776342131</v>
+        <v>0.5326757053976344</v>
       </c>
       <c r="T91">
-        <v>9.100615407758376</v>
+        <v>10.01067694853421</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01815900952316415</v>
+        <v>0.01795724275068455</v>
       </c>
       <c r="W91">
-        <v>0.2315181055544379</v>
+        <v>0.2315656821593886</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.0907950476158208</v>
+        <v>0.08978621375342277</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8914,22 +8914,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2616766844832131</v>
+        <v>0.2635766844832131</v>
       </c>
       <c r="C92">
-        <v>-2.975994393520955</v>
+        <v>-3.069596897486318</v>
       </c>
       <c r="D92">
-        <v>1.815005606479045</v>
+        <v>1.801303102513683</v>
       </c>
       <c r="E92">
-        <v>4.291</v>
+        <v>4.370900000000001</v>
       </c>
       <c r="F92">
-        <v>7.191000000000001</v>
+        <v>7.2709</v>
       </c>
       <c r="G92">
         <v>2.4</v>
@@ -8950,37 +8950,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M92">
-        <v>1.6956378</v>
+        <v>1.71447822</v>
       </c>
       <c r="N92">
-        <v>-1.543392902040817</v>
+        <v>-1.562233322040817</v>
       </c>
       <c r="O92">
-        <v>-0.3086785804081634</v>
+        <v>-0.3124466644081634</v>
       </c>
       <c r="P92">
-        <v>-1.234714321632653</v>
+        <v>-1.249786657632653</v>
       </c>
       <c r="Q92">
-        <v>0.7252856783673465</v>
+        <v>0.7102133423673467</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5326757053976344</v>
+        <v>0.5867730059973716</v>
       </c>
       <c r="T92">
-        <v>10.01067694853421</v>
+        <v>11.12297438726024</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01795724275068455</v>
+        <v>0.01775991041276494</v>
       </c>
       <c r="W92">
-        <v>0.2315656821593886</v>
+        <v>0.23161221312467</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.08978621375342277</v>
+        <v>0.08879955206382473</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8996,22 +8996,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2635766844832131</v>
+        <v>0.2654766844832132</v>
       </c>
       <c r="C93">
-        <v>-3.069596897486318</v>
+        <v>-3.162994055815767</v>
       </c>
       <c r="D93">
-        <v>1.801303102513683</v>
+        <v>1.787805944184234</v>
       </c>
       <c r="E93">
-        <v>4.370900000000001</v>
+        <v>4.450800000000001</v>
       </c>
       <c r="F93">
-        <v>7.2709</v>
+        <v>7.3508</v>
       </c>
       <c r="G93">
         <v>2.4</v>
@@ -9032,37 +9032,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M93">
-        <v>1.71447822</v>
+        <v>1.73331864</v>
       </c>
       <c r="N93">
-        <v>-1.562233322040817</v>
+        <v>-1.581073742040817</v>
       </c>
       <c r="O93">
-        <v>-0.3124466644081634</v>
+        <v>-0.3162147484081634</v>
       </c>
       <c r="P93">
-        <v>-1.249786657632653</v>
+        <v>-1.264858993632653</v>
       </c>
       <c r="Q93">
-        <v>0.7102133423673467</v>
+        <v>0.6951410063673467</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5867730059973716</v>
+        <v>0.6543946317470434</v>
       </c>
       <c r="T93">
-        <v>11.12297438726024</v>
+        <v>12.51334618566777</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01775991041276494</v>
+        <v>0.01756686790827837</v>
       </c>
       <c r="W93">
-        <v>0.23161221312467</v>
+        <v>0.231657732547228</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.08879955206382473</v>
+        <v>0.08783433954139186</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9078,22 +9078,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2654766844832132</v>
+        <v>0.2673766844832132</v>
       </c>
       <c r="C94">
-        <v>-3.162994055815767</v>
+        <v>-3.256190450141704</v>
       </c>
       <c r="D94">
-        <v>1.787805944184234</v>
+        <v>1.774509549858297</v>
       </c>
       <c r="E94">
-        <v>4.450800000000001</v>
+        <v>4.530700000000001</v>
       </c>
       <c r="F94">
-        <v>7.3508</v>
+        <v>7.430700000000001</v>
       </c>
       <c r="G94">
         <v>2.4</v>
@@ -9114,37 +9114,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M94">
-        <v>1.73331864</v>
+        <v>1.75215906</v>
       </c>
       <c r="N94">
-        <v>-1.581073742040817</v>
+        <v>-1.599914162040817</v>
       </c>
       <c r="O94">
-        <v>-0.3162147484081634</v>
+        <v>-0.3199828324081634</v>
       </c>
       <c r="P94">
-        <v>-1.264858993632653</v>
+        <v>-1.279931329632654</v>
       </c>
       <c r="Q94">
-        <v>0.6951410063673467</v>
+        <v>0.6800686703673464</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6543946317470434</v>
+        <v>0.741336721996621</v>
       </c>
       <c r="T94">
-        <v>12.51334618566777</v>
+        <v>14.3009670693346</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01756686790827837</v>
+        <v>0.01737797685550118</v>
       </c>
       <c r="W94">
-        <v>0.231657732547228</v>
+        <v>0.2317022730574728</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.08783433954139186</v>
+        <v>0.08688988427750588</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9160,22 +9160,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2673766844832132</v>
+        <v>0.2692766844832132</v>
       </c>
       <c r="C95">
-        <v>-3.256190450141704</v>
+        <v>-3.349190526803407</v>
       </c>
       <c r="D95">
-        <v>1.774509549858297</v>
+        <v>1.761409473196593</v>
       </c>
       <c r="E95">
-        <v>4.530700000000001</v>
+        <v>4.610600000000002</v>
       </c>
       <c r="F95">
-        <v>7.430700000000001</v>
+        <v>7.510600000000001</v>
       </c>
       <c r="G95">
         <v>2.4</v>
@@ -9196,37 +9196,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M95">
-        <v>1.75215906</v>
+        <v>1.77099948</v>
       </c>
       <c r="N95">
-        <v>-1.599914162040817</v>
+        <v>-1.618754582040817</v>
       </c>
       <c r="O95">
-        <v>-0.3199828324081634</v>
+        <v>-0.3237509164081634</v>
       </c>
       <c r="P95">
-        <v>-1.279931329632654</v>
+        <v>-1.295003665632654</v>
       </c>
       <c r="Q95">
-        <v>0.6800686703673464</v>
+        <v>0.6649963343673464</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.741336721996621</v>
+        <v>0.8572595089960581</v>
       </c>
       <c r="T95">
-        <v>14.3009670693346</v>
+        <v>16.68446158089037</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01737797685550118</v>
+        <v>0.01719310476129372</v>
       </c>
       <c r="W95">
-        <v>0.2317022730574728</v>
+        <v>0.2317458658972869</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.08688988427750588</v>
+        <v>0.0859655238064686</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9242,22 +9242,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2692766844832132</v>
+        <v>0.2711766844832132</v>
       </c>
       <c r="C96">
-        <v>-3.349190526803407</v>
+        <v>-3.441998601804349</v>
       </c>
       <c r="D96">
-        <v>1.761409473196593</v>
+        <v>1.748501398195651</v>
       </c>
       <c r="E96">
-        <v>4.610600000000002</v>
+        <v>4.6905</v>
       </c>
       <c r="F96">
-        <v>7.510600000000001</v>
+        <v>7.5905</v>
       </c>
       <c r="G96">
         <v>2.4</v>
@@ -9278,37 +9278,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M96">
-        <v>1.77099948</v>
+        <v>1.7898399</v>
       </c>
       <c r="N96">
-        <v>-1.618754582040817</v>
+        <v>-1.637595002040817</v>
       </c>
       <c r="O96">
-        <v>-0.3237509164081634</v>
+        <v>-0.3275190004081634</v>
       </c>
       <c r="P96">
-        <v>-1.295003665632654</v>
+        <v>-1.310076001632653</v>
       </c>
       <c r="Q96">
-        <v>0.6649963343673464</v>
+        <v>0.6499239983673466</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8572595089960581</v>
+        <v>1.01955141079527</v>
       </c>
       <c r="T96">
-        <v>16.68446158089037</v>
+        <v>20.02135389706845</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01719310476129372</v>
+        <v>0.01701212471117484</v>
       </c>
       <c r="W96">
-        <v>0.2317458658972869</v>
+        <v>0.231788540993105</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.0859655238064686</v>
+        <v>0.08506062355587418</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9324,22 +9324,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2711766844832132</v>
+        <v>0.2730766844832132</v>
       </c>
       <c r="C97">
-        <v>-3.441998601804349</v>
+        <v>-3.53461886555313</v>
       </c>
       <c r="D97">
-        <v>1.748501398195651</v>
+        <v>1.735781134446871</v>
       </c>
       <c r="E97">
-        <v>4.6905</v>
+        <v>4.7704</v>
       </c>
       <c r="F97">
-        <v>7.5905</v>
+        <v>7.670400000000001</v>
       </c>
       <c r="G97">
         <v>2.4</v>
@@ -9360,37 +9360,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M97">
-        <v>1.7898399</v>
+        <v>1.80868032</v>
       </c>
       <c r="N97">
-        <v>-1.637595002040817</v>
+        <v>-1.656435422040817</v>
       </c>
       <c r="O97">
-        <v>-0.3275190004081634</v>
+        <v>-0.3312870844081634</v>
       </c>
       <c r="P97">
-        <v>-1.310076001632653</v>
+        <v>-1.325148337632653</v>
       </c>
       <c r="Q97">
-        <v>0.6499239983673466</v>
+        <v>0.6348516623673466</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.01955141079527</v>
+        <v>1.262989263494088</v>
       </c>
       <c r="T97">
-        <v>20.02135389706845</v>
+        <v>25.02669237133558</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01701212471117484</v>
+        <v>0.01683491507876676</v>
       </c>
       <c r="W97">
-        <v>0.231788540993105</v>
+        <v>0.2318303270244268</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.08506062355587418</v>
+        <v>0.08417457539383377</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9406,22 +9406,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2730766844832132</v>
+        <v>0.2749766844832132</v>
       </c>
       <c r="C98">
-        <v>-3.534618865553129</v>
+        <v>-3.627055387398962</v>
       </c>
       <c r="D98">
-        <v>1.735781134446872</v>
+        <v>1.723244612601038</v>
       </c>
       <c r="E98">
-        <v>4.7704</v>
+        <v>4.850300000000001</v>
       </c>
       <c r="F98">
-        <v>7.6704</v>
+        <v>7.7503</v>
       </c>
       <c r="G98">
         <v>2.4</v>
@@ -9442,37 +9442,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M98">
-        <v>1.80868032</v>
+        <v>1.82752074</v>
       </c>
       <c r="N98">
-        <v>-1.656435422040817</v>
+        <v>-1.675275842040817</v>
       </c>
       <c r="O98">
-        <v>-0.3312870844081633</v>
+        <v>-0.3350551684081634</v>
       </c>
       <c r="P98">
-        <v>-1.325148337632653</v>
+        <v>-1.340220673632653</v>
       </c>
       <c r="Q98">
-        <v>0.6348516623673466</v>
+        <v>0.6197793263673466</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.262989263494085</v>
+        <v>1.668719017992114</v>
       </c>
       <c r="T98">
-        <v>25.02669237133551</v>
+        <v>33.36892316178069</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01683491507876677</v>
+        <v>0.01666135925321247</v>
       </c>
       <c r="W98">
-        <v>0.2318303270244268</v>
+        <v>0.2318712514880925</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.08417457539383377</v>
+        <v>0.0833067962660623</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9488,22 +9488,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2749766844832132</v>
+        <v>0.2768766844832132</v>
       </c>
       <c r="C99">
-        <v>-3.627055387398962</v>
+        <v>-3.719312119972033</v>
       </c>
       <c r="D99">
-        <v>1.723244612601038</v>
+        <v>1.710887880027968</v>
       </c>
       <c r="E99">
-        <v>4.850300000000001</v>
+        <v>4.930200000000001</v>
       </c>
       <c r="F99">
-        <v>7.7503</v>
+        <v>7.8302</v>
       </c>
       <c r="G99">
         <v>2.4</v>
@@ -9524,37 +9524,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M99">
-        <v>1.82752074</v>
+        <v>1.84636116</v>
       </c>
       <c r="N99">
-        <v>-1.675275842040817</v>
+        <v>-1.694116262040817</v>
       </c>
       <c r="O99">
-        <v>-0.3350551684081634</v>
+        <v>-0.3388232524081634</v>
       </c>
       <c r="P99">
-        <v>-1.340220673632653</v>
+        <v>-1.355293009632653</v>
       </c>
       <c r="Q99">
-        <v>0.6197793263673466</v>
+        <v>0.6047069903673465</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.668719017992114</v>
+        <v>2.48017852698817</v>
       </c>
       <c r="T99">
-        <v>33.36892316178069</v>
+        <v>50.05338474267104</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01666135925321247</v>
+        <v>0.01649134538328173</v>
       </c>
       <c r="W99">
-        <v>0.2318712514880925</v>
+        <v>0.2319113407586222</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.0833067962660623</v>
+        <v>0.0824567269164086</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9570,22 +9570,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2768766844832132</v>
+        <v>0.2787766844832132</v>
       </c>
       <c r="C100">
-        <v>-3.719312119972033</v>
+        <v>-3.811392903338442</v>
       </c>
       <c r="D100">
-        <v>1.710887880027968</v>
+        <v>1.698707096661559</v>
       </c>
       <c r="E100">
-        <v>4.930200000000001</v>
+        <v>5.0101</v>
       </c>
       <c r="F100">
-        <v>7.8302</v>
+        <v>7.9101</v>
       </c>
       <c r="G100">
         <v>2.4</v>
@@ -9606,37 +9606,37 @@
         <v>0.1522448979591835</v>
       </c>
       <c r="M100">
-        <v>1.84636116</v>
+        <v>1.86520158</v>
       </c>
       <c r="N100">
-        <v>-1.694116262040817</v>
+        <v>-1.712956682040817</v>
       </c>
       <c r="O100">
-        <v>-0.3388232524081634</v>
+        <v>-0.3425913364081634</v>
       </c>
       <c r="P100">
-        <v>-1.355293009632653</v>
+        <v>-1.370365345632653</v>
       </c>
       <c r="Q100">
-        <v>0.6047069903673465</v>
+        <v>0.5896346543673467</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.48017852698817</v>
+        <v>4.91455705397634</v>
       </c>
       <c r="T100">
-        <v>50.05338474267104</v>
+        <v>100.1067694853421</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01649134538328173</v>
+        <v>0.01632476613698595</v>
       </c>
       <c r="W100">
-        <v>0.2319113407586222</v>
+        <v>0.2319506201448987</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9644,91 +9644,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.0824567269164086</v>
+        <v>0.08162383068492973</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2787766844832132</v>
-      </c>
-      <c r="C101">
-        <v>-3.811392903338442</v>
-      </c>
-      <c r="D101">
-        <v>1.698707096661559</v>
-      </c>
-      <c r="E101">
-        <v>5.0101</v>
-      </c>
-      <c r="F101">
-        <v>7.9101</v>
-      </c>
-      <c r="G101">
-        <v>2.4</v>
-      </c>
-      <c r="H101">
-        <v>5.09</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.112244897959183</v>
-      </c>
-      <c r="K101">
-        <v>1.96</v>
-      </c>
-      <c r="L101">
-        <v>0.1522448979591835</v>
-      </c>
-      <c r="M101">
-        <v>1.86520158</v>
-      </c>
-      <c r="N101">
-        <v>-1.712956682040817</v>
-      </c>
-      <c r="O101">
-        <v>-0.3425913364081634</v>
-      </c>
-      <c r="P101">
-        <v>-1.370365345632653</v>
-      </c>
-      <c r="Q101">
-        <v>0.5896346543673467</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.91455705397634</v>
-      </c>
-      <c r="T101">
-        <v>100.1067694853421</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01632476613698595</v>
-      </c>
-      <c r="W101">
-        <v>0.2319506201448987</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.08162383068492973</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
